--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,22 +481,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -506,49 +506,49 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This is my second time here after several years. You can get a unique experience here if you come in the afternoon before sunset. There will be millions of bats coming out of their nests.</t>
+          <t>It's hard to wf with no signal.,..</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
+          <t>its hard to wf with no signal</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
+          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
+          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
+          <t>its hard to wf with no signal</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+          <t>Batu Bintang is indeed beautiful, suitable for people who like to see sunsets/sunrises, and in the evening, sometimes we can also see lots of swiftlets flying around, it is really recommended.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,89 +607,89 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Entrance is free. The view is beautiful, especially at sunset. The food here is standard fare. The mochi is delicious, only around 5,000 rupiah. There's also accommodation nearby, with an Indomaret just a 5-minute walk away. You can also â¦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a minute walk away you can also â</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a mute walk away you can also</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,47 +701,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -753,84 +753,84 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,42 +842,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -889,89 +889,89 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>pandang bagus pantai nya rusak bebatuan doang</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,42 +983,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
+          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
+          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
+          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,136 +1030,136 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lumayan bagusaman anak main pantai</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aksesnya mudah, sangat dekat dari jalan raya, penjual makanan banyak, untuk parkir hanya satu penjaga jadi tidak banyak pungli, pantainya ada sedikit sampah sedikit yaaa</t>
+          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>aksesnya mudah sangat dekat dari jalan raya penjual makanan banyak untuk parkir hanya satu penjaga jadi tidak banyak pungli pantainya ada sedikit sampah sedikit yaaa</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['aksesnya', 'mudah', 'sangat', 'dekat', 'dari', 'jalan', 'raya', 'penjual', 'makanan', 'banyak', 'untuk', 'parkir', 'hanya', 'satu', 'penjaga', 'jadi', 'tidak', 'banyak', 'pungli', 'pantainya', 'ada', 'sedikit', 'sampah', 'sedikit', 'yaaa']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['aksesnya', 'mudah', 'jalan', 'raya', 'penjual', 'makanan', 'parkir', 'penjaga', 'pungli', 'pantainya', 'sampah', 'yaaa']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>akses mudah jalan raya jual makan parkir jaga pungli pantai sampah yaaa</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran Nuansa nya Kaya Ala-Ala Bali. Tempat nyaman aman &amp; sejuk. Kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benar-benar senggang, â¦</t>
+          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pantai twenty cipatuguran nuansa nya kaya alaala bali tempat nyaman aman sejuk kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benarbenar senggang â</t>
+          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'tempat', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'ada', 'di', 'pantai', 'seseorang', 'tidak', 'bisa', 'mengumpulkan', 'semua', 'kerang', 'yang', 'indah', 'di', 'pantai', 'aku', 'tampil', 'sebaik', 'mungkin', 'saat', 'aku', 'benarbenar', 'senggang', 'â']</t>
+          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'pantai', 'mengumpulkan', 'kerang', 'indah', 'pantai', 'tampil', 'benarbenar', 'senggang', 'â']</t>
+          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pantai twenty cipatuguran nuansa nya kaya alaala bal nyaman aman sejuk bebas setia pantai kumpul kerang indah pantai tampil benarbenar senggang</t>
+          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music. Enjoy a young coconut water while enjoying it.</t>
+          <t>Indah dan nyaman, sayang banyak pengamen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
+          <t>indah dan nyaman sayang banyak pengamen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
+          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
+          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
+          <t>indah nyaman sayang amen</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,42 +1218,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,42 +1265,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+          <t>Enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music. Enjoy a young coconut water while enjoying it.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,42 +1312,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,89 +1359,89 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+          <t>Baru bisa berkeliling disekitarnya, ga bisa masuk ke Pesanggrahan nya... Pantainya sendiri lumayan bersih sih, mungkin karena dekat Pesanggrahan. Ada free wifi yang juga cepat saat saya akses pagi2 banget</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+          <t>baru bisa berkeliling disekitarnya ga bisa masuk ke pesanggrahan nya pantainya sendiri lumayan bersih sih mungkin karena dekat pesanggrahan ada free wifi yang juga cepat saat saya akses pagi banget</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+          <t>['baru', 'bisa', 'berkeliling', 'disekitarnya', 'ga', 'bisa', 'masuk', 'ke', 'pesanggrahan', 'nya', 'pantainya', 'sendiri', 'lumayan', 'bersih', 'sih', 'mungkin', 'karena', 'dekat', 'pesanggrahan', 'ada', 'free', 'wifi', 'yang', 'juga', 'cepat', 'saat', 'saya', 'akses', 'pagi', 'banget']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+          <t>['berkeliling', 'disekitarnya', 'ga', 'masuk', 'pesanggrahan', 'nya', 'pantainya', 'lumayan', 'bersih', 'sih', 'pesanggrahan', 'free', 'wifi', 'cepat', 'akses', 'pagi', 'banget']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+          <t>keliling sekitar ga masuk pesanggrahan nya pantai lumayan bersih sih pesanggrahan free wifi cepat akses pagi banget</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,42 +1453,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Taman Bappeda</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Yuk bisa kali Pemda, dinas atau instansi terkait di rawat fasilitas umumnya.  Hasil pantauan msh banyak yg rusak dan ada pihak2 yg gak bertanggung jawab â¦</t>
+          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>yuk bisa kali pemda dinas atau instansi terkait di rawat fasilitas umumnya hasil pantauan msh banyak yg rusak dan ada pihak yg gak bertanggung jawab â</t>
+          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['yuk', 'bisa', 'kali', 'pemda', 'dinas', 'atau', 'instansi', 'terkait', 'di', 'rawat', 'fasilitas', 'umumnya', 'hasil', 'pantauan', 'msh', 'banyak', 'yg', 'rusak', 'dan', 'ada', 'pihak', 'yg', 'gak', 'bertanggung', 'jawab', 'â']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['yuk', 'kali', 'pemda', 'dinas', 'instansi', 'terkait', 'rawat', 'fasilitas', 'hasil', 'pantauan', 'msh', 'yg', 'rusak', 'yg', 'gak', 'bertanggung', 'â']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>yuk kali pemda dinas instansi kait rawat fasilitas hasil pantau msh yg rusak yg gak tanggung</t>
+          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1547,42 +1547,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1594,42 +1594,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1641,12 +1641,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
@@ -1693,37 +1693,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
+          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
+          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
+          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
+          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
+          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,42 +1782,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>This is my second time here after several years. You can get a unique experience here if you come in the afternoon before sunset. There will be millions of bats coming out of their nests.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1834,84 +1834,84 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The place is beautiful at sunset..that's the best time to take pictures hehe</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1970,42 +1970,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The place is comfortable, cool, the toilet is always clean. The prayer clothes in the mosque are fragrant and clean. There are many vendors selling unique and cheap snacks, and the taste is also delicious.</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,12 +2017,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
+          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2064,12 +2064,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Panorama pantai yang sangat indah nyaman di lihat asik dan mempesona.. Bisa melatih bakat diri untuk yang bisa surfing | selancar di suasana pantai citepus cocok untuk wisata yang mau berkunjung kesini..</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>panorama pantai yang sangat indah nyaman di lihat asik dan mempesona bisa melatih bakat diri untuk yang bisa surfing selancar di suasana pantai citepus cocok untuk wisata yang mau berkunjung kesini</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['panorama', 'pantai', 'yang', 'sangat', 'indah', 'nyaman', 'di', 'lihat', 'asik', 'dan', 'mempesona', 'bisa', 'melatih', 'bakat', 'diri', 'untuk', 'yang', 'bisa', 'surfing', 'selancar', 'di', 'suasana', 'pantai', 'citepus', 'cocok', 'untuk', 'wisata', 'yang', 'mau', 'berkunjung', 'kesini']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['panorama', 'pantai', 'indah', 'nyaman', 'lihat', 'asik', 'mempesona', 'melatih', 'bakat', 'surfing', 'selancar', 'suasana', 'pantai', 'citepus', 'cocok', 'wisata', 'berkunjung', 'kesini']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>panorama pantai indah nyaman lihat asik pesona latih bakat surfing selancar suasana pantai citepus cocok wisata kunjung kesini</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2111,42 +2111,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
+          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2198,54 +2198,54 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
+          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
+          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
+          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -2257,37 +2257,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,42 +2299,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2346,42 +2346,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
+          <t>The place is beautiful at sunset..that's the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
+          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
+          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
+          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
+          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,42 +2393,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Entrance is free. The view is beautiful, especially at sunset. The food here is standard fare. The mochi is delicious, only around 5,000 rupiah. There's also accommodation nearby, with an Indomaret just a 5-minute walk away. You can also â¦</t>
+          <t>Come on Tuesday at 5 o'clock, entry is free, just pay 5 thousand for parking. Watch the fishermen set sail. Enjoy the sunset. I like it, I like it.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a minute walk away you can also â</t>
+          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
+          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
+          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a mute walk away you can also</t>
+          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
+          <t>Pantai Twenty Cipatuguran Nuansa nya Kaya Ala-Ala Bali. Tempat nyaman aman &amp; sejuk. Kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benar-benar senggang, â¦</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2502,22 +2502,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
+          <t>pantai twenty cipatuguran nuansa nya kaya alaala bali tempat nyaman aman sejuk kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benarbenar senggang â</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'tempat', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'ada', 'di', 'pantai', 'seseorang', 'tidak', 'bisa', 'mengumpulkan', 'semua', 'kerang', 'yang', 'indah', 'di', 'pantai', 'aku', 'tampil', 'sebaik', 'mungkin', 'saat', 'aku', 'benarbenar', 'senggang', 'â']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'pantai', 'mengumpulkan', 'kerang', 'indah', 'pantai', 'tampil', 'benarbenar', 'senggang', 'â']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
+          <t>pantai twenty cipatuguran nuansa nya kaya alaala bal nyaman aman sejuk bebas setia pantai kumpul kerang indah pantai tampil benarbenar senggang</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2534,89 +2534,89 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
+          <t>Karang Pamulang Beach, Bunga Ayu Seaside Resort Is a friendly, beautiful beach</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
+          <t>karang pamulang beach bunga ayu seaside resort is a friendly beautiful beach</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['ga', 'ada', 'pungli', 'tapi', 'kalo', 'mau', 'mesen', 'makanan', 'alangkah', 'baiknya', 'tanya', 'harga', 'dulu', 'soalnya', 'main', 'getok', 'harga']</t>
+          <t>['karang', 'pamulang', 'beach', 'bunga', 'ayu', 'seaside', 'resort', 'is', 'a', 'friendly', 'beautiful', 'beach']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['ga', 'pungli', 'kalo', 'mesen', 'makanan', 'alangkah', 'baiknya', 'harga', 'main', 'getok', 'harga']</t>
+          <t>['karang', 'pamulang', 'beach', 'bunga', 'ayu', 'seaside', 'resort', 'is', 'a', 'friendly', 'beautiful', 'beach']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ga pungli kalo mesen makan alangkah baik harga main getok harga</t>
+          <t>karang pamulang beach bunga ayu seaside resort is a friendly beautiful beach</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2628,42 +2628,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2675,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2722,136 +2722,136 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Indah dan nyaman, sayang banyak pengamen</t>
+          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>indah dan nyaman sayang banyak pengamen</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>indah nyaman sayang amen</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
+          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
+          <t>lumayan bagusaman untuk anak main dipantainya</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
+          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
+          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
+          <t>lumayan bagusaman anak main pantai</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2863,59 +2863,59 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2962,37 +2962,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Untuk tgl 16 mei 2025 strukturnya untuk sebagian masih sedang dalam perbaikan. Toilet yg tersedia di dekat alun2 untuk yang perempuan sudah tidak ada kunci nya. Dan kebetulan juga waktu saya berkunjung stand pedagang dan pameran sudah siap â¦</t>
+          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>untuk tgl mei strukturnya untuk sebagian masih sedang dalam perbaikan toilet yg tersedia di dekat alun untuk yang perempuan sudah tidak ada kunci nya dan kebetulan juga waktu saya berkunjung stand pedagang dan pameran sudah siap â</t>
+          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['untuk', 'tgl', 'mei', 'strukturnya', 'untuk', 'sebagian', 'masih', 'sedang', 'dalam', 'perbaikan', 'toilet', 'yg', 'tersedia', 'di', 'dekat', 'alun', 'untuk', 'yang', 'perempuan', 'sudah', 'tidak', 'ada', 'kunci', 'nya', 'dan', 'kebetulan', 'juga', 'waktu', 'saya', 'berkunjung', 'stand', 'pedagang', 'dan', 'pameran', 'sudah', 'siap', 'â']</t>
+          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['tgl', 'mei', 'strukturnya', 'perbaikan', 'toilet', 'yg', 'tersedia', 'alun', 'perempuan', 'kunci', 'nya', 'berkunjung', 'stand', 'pedagang', 'pameran', 'â']</t>
+          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>tgl mei struktur baik toilet yg sedia alun perempuan kunci nya kunjung stand dagang pamer</t>
+          <t>rapih tata buka pagar seng</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3004,42 +3004,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
+          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
+          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
+          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
+          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
+          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3051,42 +3051,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3098,42 +3098,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3145,12 +3145,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The view is quite beautiful, and facilities like resting huts and bathrooms are also available. However, please don't overcharge the bathroom/toilet facilities. Just to use them, we had to pay 5,000 rupiah. Just to relieve ourselves.</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3160,22 +3160,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>the view is quite beautiful and facilities like resting huts and bathrooms are also available however please dont overcharge the bathroomtoilet facilities just to use them we had to pay rupiah just to relieve ourselves</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'beautiful', 'and', 'facilities', 'like', 'resting', 'huts', 'and', 'bathrooms', 'are', 'also', 'available', 'however', 'please', 'dont', 'overcharge', 'the', 'bathroomtoilet', 'facilities', 'just', 'to', 'use', 'them', 'we', 'had', 'to', 'pay', 'rupiah', 'just', 'to', 'relieve', 'ourselves']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'beautiful', 'and', 'facilities', 'like', 'resting', 'huts', 'and', 'bathrooms', 'are', 'also', 'available', 'however', 'please', 'dont', 'overcharge', 'the', 'bathroomtoilet', 'facilities', 'just', 'to', 'use', 'them', 'we', 'had', 'to', 'pay', 'rupiah', 'just', 'to', 'relieve', 'ourselves']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>the view is quite beautiful and facilities like resting huts and bathrooms are also available however please dont overcharge the bathroomtoilet facilities just to use them we had to pay rupiah just to relieve ourselves</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3192,89 +3192,89 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
+          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3286,42 +3286,42 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3333,89 +3333,89 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The beach is comfortable, clean, there are huts to enjoy the beach atmosphere, in short it's really great, there are lots of food menus</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>the beach is comfortable clean there are huts to enjoy the beach atmosphere in short its really great there are lots of food menus</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'comfortable', 'clean', 'there', 'are', 'huts', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'in', 'short', 'its', 'really', 'great', 'there', 'are', 'lots', 'of', 'food', 'menus']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'comfortable', 'clean', 'there', 'are', 'huts', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'in', 'short', 'its', 'really', 'great', 'there', 'are', 'lots', 'of', 'food', 'menus']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>the beach is comfortable clean there are huts to enjoy the beach atmosphere in short its really great there are lots of food nus</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pantai Citepus Tempat Nyaman Aman &amp; Ramai Pengunjung. Puisi Pantai "Kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benar-benar senggang, saat liburan, â¦</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>pantai citepus tempat nyaman aman ramai pengunjung puisi pantai kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benarbenar senggang saat liburan â</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>['pantai', 'citepus', 'tempat', 'nyaman', 'aman', 'ramai', 'pengunjung', 'puisi', 'pantai', 'kebebasan', 'setia', 'ada', 'di', 'pantai', 'seseorang', 'tidak', 'bisa', 'mengumpulkan', 'semua', 'kerang', 'yang', 'indah', 'di', 'pantai', 'aku', 'tampil', 'sebaik', 'mungkin', 'saat', 'aku', 'benarbenar', 'senggang', 'saat', 'liburan', 'â']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>['pantai', 'citepus', 'nyaman', 'aman', 'ramai', 'pengunjung', 'puisi', 'pantai', 'kebebasan', 'setia', 'pantai', 'mengumpulkan', 'kerang', 'indah', 'pantai', 'tampil', 'benarbenar', 'senggang', 'liburan', 'â']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>pantai citepus nyaman aman ramai unjung puisi pantai bebas setia pantai kumpul kerang indah pantai tampil benarbenar senggang libur</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3427,42 +3427,42 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
+          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3474,12 +3474,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Enak cuaca cerah, hanya pantai kotor maret kami akan beekunjung semoga pantainya sudah bersih</t>
+          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3489,22 +3489,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>enak cuaca cerah hanya pantai kotor maret kami akan beekunjung semoga pantainya sudah bersih</t>
+          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>['enak', 'cuaca', 'cerah', 'hanya', 'pantai', 'kotor', 'maret', 'kami', 'akan', 'beekunjung', 'semoga', 'pantainya', 'sudah', 'bersih']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>['enak', 'cuaca', 'cerah', 'pantai', 'kotor', 'maret', 'beekunjung', 'semoga', 'pantainya', 'bersih']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>enak cuaca cerah pantai kotor maret beekunjung moga pantai bersih</t>
+          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3514,49 +3514,49 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3568,12 +3568,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3607,431 +3607,6 @@
         </is>
       </c>
       <c r="I68" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Pantai Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Parking and beach entrance fees are standard, and the parking area is very spacious. Prices for food carts are about the same as in Jakarta, so it's still safe. Renting a pavilion is quite expensive, at 30,000 Rupiah per hour. Toilet use is 5,000 Rupiah per person.</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>parking and beach entrance fees are standard and the parking area is very spacious prices for food carts are about the same as in jakarta so its still safe renting a pavilion is quite expensive at rupiah per hour toilet use is rupiah per person</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>['parking', 'and', 'beach', 'entrance', 'fees', 'are', 'standard', 'and', 'the', 'parking', 'area', 'is', 'very', 'spacious', 'prices', 'for', 'food', 'carts', 'are', 'about', 'the', 'same', 'as', 'in', 'jakarta', 'so', 'its', 'still', 'safe', 'renting', 'a', 'pavilion', 'is', 'quite', 'expensive', 'at', 'rupiah', 'per', 'hour', 'toilet', 'use', 'is', 'rupiah', 'per', 'person']</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>['parking', 'and', 'beach', 'entrance', 'fees', 'are', 'standard', 'and', 'the', 'parking', 'area', 'is', 'very', 'spacious', 'prices', 'for', 'food', 'carts', 'are', 'about', 'the', 'same', 'as', 'in', 'jakarta', 'so', 'its', 'still', 'safe', 'renting', 'a', 'pavilion', 'is', 'quite', 'expensive', 'at', 'rupiah', 'hour', 'toilet', 'use', 'is', 'rupiah', 'person']</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>parking and beach entrance fees are standard and the parking area is very spacious prices for food carts are about the same as in jakarta so its still safe renting a pavilion is quite expensive at rupiah hour toilet use is rupiah person</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Love the bamboo chairs lined up along this beach. No rental fees; just buy a drink or a young coconut. The view is breathtaking, overlooking the beach and coral reef. It's especially great if you want to watch the sunset while relaxing. There's also a music festival on Saturday nights, which entertains tourists.</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Alun2 TerBersihhh yg pernah saya kunjungi, kerennnn pertahankan</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>alun terbersihhh yg pernah saya kunjungi kerennnn pertahankan</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>['alun', 'terbersihhh', 'yg', 'pernah', 'saya', 'kunjungi', 'kerennnn', 'pertahankan']</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>['alun', 'terbersihhh', 'yg', 'kunjungi', 'kerennnn', 'pertahankan']</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>alun terbersihhh yg kunjung kerennnn tahan</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Pantai Citepus</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað-ð-, dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>PANTAI CIBANGBAN</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Pantainya kurang terawat,parkirnya berntakan</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>pantainya kurang terawatparkirnya berntakan</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>pantai terawatparkirnya berntakan</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Batu Bintang is indeed beautiful, suitable for people who like to see sunsets/sunrises, and in the evening, sometimes we can also see lots of swiftlets flying around, it is really recommended.</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,59 +466,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>It's hard to wf with no signal.,..</t>
+          <t>Enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music. Enjoy a young coconut water while enjoying it.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>its hard to wf with no signal</t>
+          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
+          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
+          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>its hard to wf with no signal</t>
+          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,96 +553,96 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Batu Bintang is indeed beautiful, suitable for people who like to see sunsets/sunrises, and in the evening, sometimes we can also see lots of swiftlets flying around, it is really recommended.</t>
+          <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
+          <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
+          <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
+          <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
+          <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Entrance is free. The view is beautiful, especially at sunset. The food here is standard fare. The mochi is delicious, only around 5,000 rupiah. There's also accommodation nearby, with an Indomaret just a 5-minute walk away. You can also â¦</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a minute walk away you can also â</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a mute walk away you can also</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,42 +701,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,183 +795,183 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>Come on Tuesday at 5 o'clock, entry is free, just pay 5 thousand for parking. Watch the fishermen set sail. Enjoy the sunset. I like it, I like it.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>pandang bagus pantai nya rusak bebatuan doang</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Taman Bappeda</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>Yuk bisa kali Pemda, dinas atau instansi terkait di rawat fasilitas umumnya.  Hasil pantauan msh banyak yg rusak dan ada pihak2 yg gak bertanggung jawab â¦</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>yuk bisa kali pemda dinas atau instansi terkait di rawat fasilitas umumnya hasil pantauan msh banyak yg rusak dan ada pihak yg gak bertanggung jawab â</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['yuk', 'bisa', 'kali', 'pemda', 'dinas', 'atau', 'instansi', 'terkait', 'di', 'rawat', 'fasilitas', 'umumnya', 'hasil', 'pantauan', 'msh', 'banyak', 'yg', 'rusak', 'dan', 'ada', 'pihak', 'yg', 'gak', 'bertanggung', 'jawab', 'â']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['yuk', 'kali', 'pemda', 'dinas', 'instansi', 'terkait', 'rawat', 'fasilitas', 'hasil', 'pantauan', 'msh', 'yg', 'rusak', 'yg', 'gak', 'bertanggung', 'â']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>yuk kali pemda dinas instansi kait rawat fasilitas hasil pantau msh yg rusak yg gak tanggung</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,42 +983,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
+          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,59 +1030,59 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Alun2 TerBersihhh yg pernah saya kunjungi, kerennnn pertahankan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>alun terbersihhh yg pernah saya kunjungi kerennnn pertahankan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['alun', 'terbersihhh', 'yg', 'pernah', 'saya', 'kunjungi', 'kerennnn', 'pertahankan']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['alun', 'terbersihhh', 'yg', 'kunjungi', 'kerennnn', 'pertahankan']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>alun terbersihhh yg kunjung kerennnn tahan</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,59 +1124,59 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indah dan nyaman, sayang banyak pengamen</t>
+          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>indah dan nyaman sayang banyak pengamen</t>
+          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
+          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
+          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>indah nyaman sayang amen</t>
+          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1211,19 +1211,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tugu nyah udah di pindahin</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tugu nyah udah di pindahin</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tugu nyah udah pindahin</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1265,89 +1265,89 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music. Enjoy a young coconut water while enjoying it.</t>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Pantainya kurang terawat,parkirnya berntakan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>pantainya kurang terawatparkirnya berntakan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>pantai terawatparkirnya berntakan</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,59 +1359,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Baru bisa berkeliling disekitarnya, ga bisa masuk ke Pesanggrahan nya... Pantainya sendiri lumayan bersih sih, mungkin karena dekat Pesanggrahan. Ada free wifi yang juga cepat saat saya akses pagi2 banget</t>
+          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>baru bisa berkeliling disekitarnya ga bisa masuk ke pesanggrahan nya pantainya sendiri lumayan bersih sih mungkin karena dekat pesanggrahan ada free wifi yang juga cepat saat saya akses pagi banget</t>
+          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['baru', 'bisa', 'berkeliling', 'disekitarnya', 'ga', 'bisa', 'masuk', 'ke', 'pesanggrahan', 'nya', 'pantainya', 'sendiri', 'lumayan', 'bersih', 'sih', 'mungkin', 'karena', 'dekat', 'pesanggrahan', 'ada', 'free', 'wifi', 'yang', 'juga', 'cepat', 'saat', 'saya', 'akses', 'pagi', 'banget']</t>
+          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['berkeliling', 'disekitarnya', 'ga', 'masuk', 'pesanggrahan', 'nya', 'pantainya', 'lumayan', 'bersih', 'sih', 'pesanggrahan', 'free', 'wifi', 'cepat', 'akses', 'pagi', 'banget']</t>
+          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>keliling sekitar ga masuk pesanggrahan nya pantai lumayan bersih sih pesanggrahan free wifi cepat akses pagi banget</t>
+          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
+          <t>The view is quite beautiful, and facilities like resting huts and bathrooms are also available. However, please don't overcharge the bathroom/toilet facilities. Just to use them, we had to pay 5,000 rupiah. Just to relieve ourselves.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
+          <t>the view is quite beautiful and facilities like resting huts and bathrooms are also available however please dont overcharge the bathroomtoilet facilities just to use them we had to pay rupiah just to relieve ourselves</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
+          <t>['the', 'view', 'is', 'quite', 'beautiful', 'and', 'facilities', 'like', 'resting', 'huts', 'and', 'bathrooms', 'are', 'also', 'available', 'however', 'please', 'dont', 'overcharge', 'the', 'bathroomtoilet', 'facilities', 'just', 'to', 'use', 'them', 'we', 'had', 'to', 'pay', 'rupiah', 'just', 'to', 'relieve', 'ourselves']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
+          <t>['the', 'view', 'is', 'quite', 'beautiful', 'and', 'facilities', 'like', 'resting', 'huts', 'and', 'bathrooms', 'are', 'also', 'available', 'however', 'please', 'dont', 'overcharge', 'the', 'bathroomtoilet', 'facilities', 'just', 'to', 'use', 'them', 'we', 'had', 'to', 'pay', 'rupiah', 'just', 'to', 'relieve', 'ourselves']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
+          <t>the view is quite beautiful and facilities like resting huts and bathrooms are also available however please dont overcharge the bathroomtoilet facilities just to use them we had to pay rupiah just to relieve ourselves</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1458,37 +1458,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
+          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Muara Citepus Palabuhanratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
+          <t>The beach, which is located in Ratu Harbor, has become a tourist attraction, so it is more tidy and equipped with umbrellas and visitor seats.  Rinses and toilets are available and well managed .  Many sellers of young coconut, food and â¦</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
+          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and â</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
+          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
+          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
+          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
+          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1609,22 +1609,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
+          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
+          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
+          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
+          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1641,136 +1641,136 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>A beautiful beach with a stunning sunset view. Access to the location is adequate for both two- and four-wheeled vehicles, via the national road from Cigombong or the Bocimi toll road (when it is permanently opened). My trip from Bogor via â¦</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>a beautiful beach with a stunning sunset view access to the location is adequate for both two and fourwheeled vehicles via the national road from cigombong or the bocimi toll road when it is permanently opened my trip from bogor via â</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['a', 'beautiful', 'beach', 'with', 'a', 'stunning', 'sunset', 'view', 'access', 'to', 'the', 'location', 'is', 'adequate', 'for', 'both', 'two', 'and', 'fourwheeled', 'vehicles', 'via', 'the', 'national', 'road', 'from', 'cigombong', 'or', 'the', 'bocimi', 'toll', 'road', 'when', 'it', 'is', 'permanently', 'opened', 'my', 'trip', 'from', 'bogor', 'via', 'â']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['a', 'beautiful', 'beach', 'with', 'a', 'stunning', 'sunset', 'view', 'access', 'to', 'the', 'location', 'is', 'adequate', 'for', 'both', 'two', 'and', 'fourwheeled', 'vehicles', 'via', 'the', 'national', 'road', 'from', 'cigombong', 'or', 'the', 'bocimi', 'toll', 'road', 'when', 'it', 'is', 'permanently', 'opened', 'my', 'trip', 'from', 'bogor', 'via', 'â']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>a beautiful beach with a stunning sunset view access to the location is adequate for both two and fourwheeled vehicles via the national road from cigombong or the bocimi toll road when it is permanently opened my trip from bogor via</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,42 +1782,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>This is my second time here after several years. You can get a unique experience here if you come in the afternoon before sunset. There will be millions of bats coming out of their nests.</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,47 +1829,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1891,22 +1891,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>This is my second time here after several years. You can get a unique experience here if you come in the afternoon before sunset. There will be millions of bats coming out of their nests.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2017,42 +2017,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2064,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kerennn</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2111,42 +2111,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,42 +2158,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2205,42 +2205,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,12 +2252,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
+          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2299,89 +2299,89 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The place is beautiful at sunset..that's the best time to take pictures hehe</t>
+          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
+          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
+          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,59 +2393,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Come on Tuesday at 5 o'clock, entry is free, just pay 5 thousand for parking. Watch the fishermen set sail. Enjoy the sunset. I like it, I like it.</t>
+          <t>rekomendasi untuk nongkrong buat kaula muda,cocok untuk semua umur.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
+          <t>rekomendasi untuk nongkrong buat kaula mudacocok untuk semua umur</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
+          <t>['rekomendasi', 'untuk', 'nongkrong', 'buat', 'kaula', 'mudacocok', 'untuk', 'semua', 'umur']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
+          <t>['rekomendasi', 'nongkrong', 'kaula', 'mudacocok', 'umur']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
+          <t>rekomendasi nongkrong kaula mudacocok umur</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2487,89 +2487,89 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran Nuansa nya Kaya Ala-Ala Bali. Tempat nyaman aman &amp; sejuk. Kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benar-benar senggang, â¦</t>
+          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>pantai twenty cipatuguran nuansa nya kaya alaala bali tempat nyaman aman sejuk kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benarbenar senggang â</t>
+          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'tempat', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'ada', 'di', 'pantai', 'seseorang', 'tidak', 'bisa', 'mengumpulkan', 'semua', 'kerang', 'yang', 'indah', 'di', 'pantai', 'aku', 'tampil', 'sebaik', 'mungkin', 'saat', 'aku', 'benarbenar', 'senggang', 'â']</t>
+          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'pantai', 'mengumpulkan', 'kerang', 'indah', 'pantai', 'tampil', 'benarbenar', 'senggang', 'â']</t>
+          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>pantai twenty cipatuguran nuansa nya kaya alaala bal nyaman aman sejuk bebas setia pantai kumpul kerang indah pantai tampil benarbenar senggang</t>
+          <t>pandang bagus pantai nya rusak bebatuan doang</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,42 +2581,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Karang Pamulang Beach, Bunga Ayu Seaside Resort Is a friendly, beautiful beach</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>karang pamulang beach bunga ayu seaside resort is a friendly beautiful beach</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['karang', 'pamulang', 'beach', 'bunga', 'ayu', 'seaside', 'resort', 'is', 'a', 'friendly', 'beautiful', 'beach']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['karang', 'pamulang', 'beach', 'bunga', 'ayu', 'seaside', 'resort', 'is', 'a', 'friendly', 'beautiful', 'beach']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>karang pamulang beach bunga ayu seaside resort is a friendly beautiful beach</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2628,42 +2628,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>lumayan bagusaman untuk anak main dipantainya</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>lumayan bagusaman anak main pantai</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2675,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>Parking and beach entrance fees are standard, and the parking area is very spacious. Prices for food carts are about the same as in Jakarta, so it's still safe. Renting a pavilion is quite expensive, at 30,000 Rupiah per hour. Toilet use is 5,000 Rupiah per person.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>parking and beach entrance fees are standard and the parking area is very spacious prices for food carts are about the same as in jakarta so its still safe renting a pavilion is quite expensive at rupiah per hour toilet use is rupiah per person</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['parking', 'and', 'beach', 'entrance', 'fees', 'are', 'standard', 'and', 'the', 'parking', 'area', 'is', 'very', 'spacious', 'prices', 'for', 'food', 'carts', 'are', 'about', 'the', 'same', 'as', 'in', 'jakarta', 'so', 'its', 'still', 'safe', 'renting', 'a', 'pavilion', 'is', 'quite', 'expensive', 'at', 'rupiah', 'per', 'hour', 'toilet', 'use', 'is', 'rupiah', 'per', 'person']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['parking', 'and', 'beach', 'entrance', 'fees', 'are', 'standard', 'and', 'the', 'parking', 'area', 'is', 'very', 'spacious', 'prices', 'for', 'food', 'carts', 'are', 'about', 'the', 'same', 'as', 'in', 'jakarta', 'so', 'its', 'still', 'safe', 'renting', 'a', 'pavilion', 'is', 'quite', 'expensive', 'at', 'rupiah', 'hour', 'toilet', 'use', 'is', 'rupiah', 'person']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>parking and beach entrance fees are standard and the parking area is very spacious prices for food carts are about the same as in jakarta so its still safe renting a pavilion is quite expensive at rupiah hour toilet use is rupiah person</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2722,89 +2722,89 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2816,42 +2816,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>lumayan bagusaman anak main pantai</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2863,59 +2863,59 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>If you're lucky, you can catch a sunset like this from here. Hopefully, in the future, it will be tidier and cleaner. Some spots still need more attention. ð â¦</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>if youre lucky you can catch a sunset like this from here hopefully in the future it will be tidier and cleaner some spots still need more attention ð â</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['if', 'youre', 'lucky', 'you', 'can', 'catch', 'a', 'sunset', 'like', 'this', 'from', 'here', 'hopefully', 'in', 'the', 'future', 'it', 'will', 'be', 'tidier', 'and', 'cleaner', 'some', 'spots', 'still', 'need', 'more', 'attention', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['if', 'youre', 'lucky', 'you', 'can', 'catch', 'a', 'sunset', 'like', 'this', 'from', 'here', 'hopefully', 'in', 'the', 'future', 'it', 'will', 'be', 'tidier', 'and', 'cleaner', 'some', 'spots', 'still', 'need', 'more', 'attention', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>if youre lucky you can catch a sunset like this from here hopefully in the future it will be tidier and cleaner some spots still need more attention</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2957,42 +2957,42 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>rapih tata buka pagar seng</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3004,42 +3004,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3051,42 +3051,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+          <t>Stopped by here because I was attending a friend's wedding, so there was still time so it was quite suitable for walking around. It's just that the timing wasn't right. I came around sunset when the sun was at its hottest. So there weren't â¦</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+          <t>stopped by here because i was attending a friends wedding so there was still time so it was quite suitable for walking around its just that the timing wasnt right i came around sunset when the sun was at its hottest so there werent â</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['stopped', 'by', 'here', 'because', 'i', 'was', 'attending', 'a', 'friends', 'wedding', 'so', 'there', 'was', 'still', 'time', 'so', 'it', 'was', 'quite', 'suitable', 'for', 'walking', 'around', 'its', 'just', 'that', 'the', 'timing', 'wasnt', 'right', 'i', 'came', 'around', 'sunset', 'when', 'the', 'sun', 'was', 'at', 'its', 'hottest', 'so', 'there', 'werent', 'â']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['stopped', 'by', 'here', 'because', 'i', 'was', 'attending', 'a', 'friends', 'wedding', 'so', 'there', 'was', 'still', 'time', 'so', 'it', 'was', 'quite', 'suitable', 'for', 'walking', 'around', 'its', 'just', 'that', 'the', 'timing', 'wasnt', 'right', 'i', 'came', 'around', 'sunset', 'when', 'the', 'sun', 'was', 'at', 'its', 'hottest', 'so', 'there', 'werent', 'â']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+          <t>stopped by here because i was attending a friends wedding so there was still time so it was quite suitable for walking around its just that the timing wasnt right i came around sunset when the sun was at its hottest so there werent</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3098,42 +3098,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>The beach is located right behind the coal-fired power plant (PLTU). Entrance is 15,000 rupiah for cars and 5,000 rupiah for motorcycles. Parking is free. Facilities include shower rooms (5,000 rupiah), toilets (2,000 rupiah), and gazebos â¦</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>the beach is located right behind the coalfired power plant pltu entrance is rupiah for cars and rupiah for motorcycles parking is free facilities include shower rooms rupiah toilets rupiah and gazebos â</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['the', 'beach', 'is', 'located', 'right', 'behind', 'the', 'coalfired', 'power', 'plant', 'pltu', 'entrance', 'is', 'rupiah', 'for', 'cars', 'and', 'rupiah', 'for', 'motorcycles', 'parking', 'is', 'free', 'facilities', 'include', 'shower', 'rooms', 'rupiah', 'toilets', 'rupiah', 'and', 'gazebos', 'â']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['the', 'beach', 'is', 'located', 'right', 'behind', 'the', 'coalfired', 'power', 'plant', 'pltu', 'entrance', 'is', 'rupiah', 'for', 'cars', 'and', 'rupiah', 'for', 'motorcycles', 'parking', 'is', 'free', 'facilities', 'include', 'shower', 'rooms', 'rupiah', 'toilets', 'rupiah', 'and', 'gazebos', 'â']</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>the beach is located right behind the coalfired power plant pltu entrance is rupiah for cars and rupiah for motorcycles parking is free facilities include shower rooms rupiah toilets rupiah and gazebos</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3145,42 +3145,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3192,89 +3192,89 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
+          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
+          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
+          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
+          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
+          <t>rapih tata buka pagar seng</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3286,47 +3286,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Indah dan nyaman, sayang banyak pengamen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>indah dan nyaman sayang banyak pengamen</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>indah nyaman sayang amen</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -3380,42 +3380,42 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3427,42 +3427,42 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
+          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
+          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
+          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3474,12 +3474,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3489,22 +3489,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3521,92 +3521,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,22 +481,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -513,136 +513,136 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music. Enjoy a young coconut water while enjoying it.</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
+          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -748,12 +748,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -788,19 +788,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,22 +810,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -835,19 +835,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Come on Tuesday at 5 o'clock, entry is free, just pay 5 thousand for parking. Watch the fishermen set sail. Enjoy the sunset. I like it, I like it.</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -889,12 +889,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -904,22 +904,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>rapih tata buka pagar seng</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -936,12 +936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Taman Bappeda</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yuk bisa kali Pemda, dinas atau instansi terkait di rawat fasilitas umumnya.  Hasil pantauan msh banyak yg rusak dan ada pihak2 yg gak bertanggung jawab â¦</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -951,22 +951,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>yuk bisa kali pemda dinas atau instansi terkait di rawat fasilitas umumnya hasil pantauan msh banyak yg rusak dan ada pihak yg gak bertanggung jawab â</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['yuk', 'bisa', 'kali', 'pemda', 'dinas', 'atau', 'instansi', 'terkait', 'di', 'rawat', 'fasilitas', 'umumnya', 'hasil', 'pantauan', 'msh', 'banyak', 'yg', 'rusak', 'dan', 'ada', 'pihak', 'yg', 'gak', 'bertanggung', 'jawab', 'â']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['yuk', 'kali', 'pemda', 'dinas', 'instansi', 'terkait', 'rawat', 'fasilitas', 'hasil', 'pantauan', 'msh', 'yg', 'rusak', 'yg', 'gak', 'bertanggung', 'â']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>yuk kali pemda dinas instansi kait rawat fasilitas hasil pantau msh yg rusak yg gak tanggung</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -976,96 +976,96 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alun2 TerBersihhh yg pernah saya kunjungi, kerennnn pertahankan</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>alun terbersihhh yg pernah saya kunjungi kerennnn pertahankan</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['alun', 'terbersihhh', 'yg', 'pernah', 'saya', 'kunjungi', 'kerennnn', 'pertahankan']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['alun', 'terbersihhh', 'yg', 'kunjungi', 'kerennnn', 'pertahankan']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>alun terbersihhh yg kunjung kerennnn tahan</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,42 +1077,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1124,42 +1124,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,42 +1218,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,89 +1265,89 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pantainya kurang terawat,parkirnya berntakan</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pantainya kurang terawatparkirnya berntakan</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>pantai terawatparkirnya berntakan</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,94 +1359,94 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The view is quite beautiful, and facilities like resting huts and bathrooms are also available. However, please don't overcharge the bathroom/toilet facilities. Just to use them, we had to pay 5,000 rupiah. Just to relieve ourselves.</t>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>the view is quite beautiful and facilities like resting huts and bathrooms are also available however please dont overcharge the bathroomtoilet facilities just to use them we had to pay rupiah just to relieve ourselves</t>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'beautiful', 'and', 'facilities', 'like', 'resting', 'huts', 'and', 'bathrooms', 'are', 'also', 'available', 'however', 'please', 'dont', 'overcharge', 'the', 'bathroomtoilet', 'facilities', 'just', 'to', 'use', 'them', 'we', 'had', 'to', 'pay', 'rupiah', 'just', 'to', 'relieve', 'ourselves']</t>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'beautiful', 'and', 'facilities', 'like', 'resting', 'huts', 'and', 'bathrooms', 'are', 'also', 'available', 'however', 'please', 'dont', 'overcharge', 'the', 'bathroomtoilet', 'facilities', 'just', 'to', 'use', 'them', 'we', 'had', 'to', 'pay', 'rupiah', 'just', 'to', 'relieve', 'ourselves']</t>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>the view is quite beautiful and facilities like resting huts and bathrooms are also available however please dont overcharge the bathroomtoilet facilities just to use them we had to pay rupiah just to relieve ourselves</t>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
@@ -1458,37 +1458,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Muara Citepus Palabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The beach, which is located in Ratu Harbor, has become a tourist attraction, so it is more tidy and equipped with umbrellas and visitor seats.  Rinses and toilets are available and well managed .  Many sellers of young coconut, food and â¦</t>
+          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and â</t>
+          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
+          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
+          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and</t>
+          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1547,42 +1547,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Susah wf.sama signal.,..</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1594,42 +1594,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
+          <t>My friend's hometown, which is like my own village, really likes the cool and fresh atmosphere of Pelabuhan Ratu. Whether you want to go to the nearby beach or see the mountains, it's the perfect healing spot in southern West Java, not too far from Jakarta. Going forward, we'll try to keep it clean, especially by not littering.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
+          <t>my friends hometown which is like my own village really likes the cool and fresh atmosphere of pelabuhan ratu whether you want to go to the nearby beach or see the mountains its the perfect healing spot in southern west java not too far from jakarta going forward well try to keep it clean especially by not littering</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
+          <t>['my', 'friends', 'hometown', 'which', 'is', 'like', 'my', 'own', 'village', 'really', 'likes', 'the', 'cool', 'and', 'fresh', 'atmosphere', 'of', 'pelabuhan', 'ratu', 'whether', 'you', 'want', 'to', 'go', 'to', 'the', 'nearby', 'beach', 'or', 'see', 'the', 'mountains', 'its', 'the', 'perfect', 'healing', 'spot', 'in', 'southern', 'west', 'java', 'not', 'too', 'far', 'from', 'jakarta', 'going', 'forward', 'well', 'try', 'to', 'keep', 'it', 'clean', 'especially', 'by', 'not', 'littering']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
+          <t>['my', 'friends', 'hometown', 'which', 'is', 'like', 'my', 'own', 'village', 'really', 'likes', 'the', 'cool', 'and', 'fresh', 'atmosphere', 'of', 'pelabuhan', 'ratu', 'whether', 'you', 'want', 'to', 'go', 'to', 'the', 'nearby', 'beach', 'or', 'see', 'the', 'mountains', 'its', 'the', 'perfect', 'healing', 'spot', 'in', 'southern', 'west', 'java', 'not', 'too', 'far', 'from', 'jakarta', 'going', 'forward', 'well', 'try', 'to', 'keep', 'it', 'clean', 'especially', 'by', 'not', 'littering']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
+          <t>my friends hometown which is like my own village really likes the cool and fresh atmosphere of labuh ratu whether you want to go to the nearby beach or see the mountains its the perfect healing spot in southern west java not too far from jakarta going forward well try to keep it clean especially by not littering</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1641,12 +1641,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A beautiful beach with a stunning sunset view. Access to the location is adequate for both two- and four-wheeled vehicles, via the national road from Cigombong or the Bocimi toll road (when it is permanently opened). My trip from Bogor via â¦</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>a beautiful beach with a stunning sunset view access to the location is adequate for both two and fourwheeled vehicles via the national road from cigombong or the bocimi toll road when it is permanently opened my trip from bogor via â</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['a', 'beautiful', 'beach', 'with', 'a', 'stunning', 'sunset', 'view', 'access', 'to', 'the', 'location', 'is', 'adequate', 'for', 'both', 'two', 'and', 'fourwheeled', 'vehicles', 'via', 'the', 'national', 'road', 'from', 'cigombong', 'or', 'the', 'bocimi', 'toll', 'road', 'when', 'it', 'is', 'permanently', 'opened', 'my', 'trip', 'from', 'bogor', 'via', 'â']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['a', 'beautiful', 'beach', 'with', 'a', 'stunning', 'sunset', 'view', 'access', 'to', 'the', 'location', 'is', 'adequate', 'for', 'both', 'two', 'and', 'fourwheeled', 'vehicles', 'via', 'the', 'national', 'road', 'from', 'cigombong', 'or', 'the', 'bocimi', 'toll', 'road', 'when', 'it', 'is', 'permanently', 'opened', 'my', 'trip', 'from', 'bogor', 'via', 'â']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>a beautiful beach with a stunning sunset view access to the location is adequate for both two and fourwheeled vehicles via the national road from cigombong or the bocimi toll road when it is permanently opened my trip from bogor via</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1688,89 +1688,89 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
+          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
+          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
+          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
+          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
+          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,42 +1782,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,12 +1829,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1844,22 +1844,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1869,19 +1869,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1891,22 +1891,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1916,96 +1916,96 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kerennn</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>This is my second time here after several years. You can get a unique experience here if you come in the afternoon before sunset. There will be millions of bats coming out of their nests.</t>
+          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
+          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
+          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,42 +2017,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2064,89 +2064,89 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Pantainya kurang terawat,parkirnya berntakan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>pantainya kurang terawatparkirnya berntakan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pantai terawatparkirnya berntakan</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2205,59 +2205,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2299,89 +2299,89 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
+          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>lumayan bagusaman untuk anak main dipantainya</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>lumayan bagusaman anak main pantai</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,47 +2393,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -2445,37 +2445,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>rekomendasi untuk nongkrong buat kaula muda,cocok untuk semua umur.</t>
+          <t>Palabuhan Ratu Square: A Strategic Location with a Cozy Atmosphere Palabuhan Ratu Square is a must-visit destination in Sukabumi. Its strategic location, right in the city center and directly adjacent to the Palabuhan Ratu â¦</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rekomendasi untuk nongkrong buat kaula mudacocok untuk semua umur</t>
+          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu â</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['rekomendasi', 'untuk', 'nongkrong', 'buat', 'kaula', 'mudacocok', 'untuk', 'semua', 'umur']</t>
+          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['rekomendasi', 'nongkrong', 'kaula', 'mudacocok', 'umur']</t>
+          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>rekomendasi nongkrong kaula mudacocok umur</t>
+          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2487,89 +2487,89 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>pandang bagus pantai nya rusak bebatuan doang</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>It's really fun, not too crowded and still clean, the water is cool, the waves aren't too big, perfect for swimming, then in the afternoon we went to the rocks, wow, the sunset was amazing, the food was delicious and not too expensive.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2628,42 +2628,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>lumayan bagusaman anak main pantai</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2675,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Parking and beach entrance fees are standard, and the parking area is very spacious. Prices for food carts are about the same as in Jakarta, so it's still safe. Renting a pavilion is quite expensive, at 30,000 Rupiah per hour. Toilet use is 5,000 Rupiah per person.</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>parking and beach entrance fees are standard and the parking area is very spacious prices for food carts are about the same as in jakarta so its still safe renting a pavilion is quite expensive at rupiah per hour toilet use is rupiah per person</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['parking', 'and', 'beach', 'entrance', 'fees', 'are', 'standard', 'and', 'the', 'parking', 'area', 'is', 'very', 'spacious', 'prices', 'for', 'food', 'carts', 'are', 'about', 'the', 'same', 'as', 'in', 'jakarta', 'so', 'its', 'still', 'safe', 'renting', 'a', 'pavilion', 'is', 'quite', 'expensive', 'at', 'rupiah', 'per', 'hour', 'toilet', 'use', 'is', 'rupiah', 'per', 'person']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['parking', 'and', 'beach', 'entrance', 'fees', 'are', 'standard', 'and', 'the', 'parking', 'area', 'is', 'very', 'spacious', 'prices', 'for', 'food', 'carts', 'are', 'about', 'the', 'same', 'as', 'in', 'jakarta', 'so', 'its', 'still', 'safe', 'renting', 'a', 'pavilion', 'is', 'quite', 'expensive', 'at', 'rupiah', 'hour', 'toilet', 'use', 'is', 'rupiah', 'person']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>parking and beach entrance fees are standard and the parking area is very spacious prices for food carts are about the same as in jakarta so its still safe renting a pavilion is quite expensive at rupiah hour toilet use is rupiah person</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2722,42 +2722,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2769,12 +2769,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Indah dan nyaman, sayang banyak pengamen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2831,22 +2831,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>indah dan nyaman sayang banyak pengamen</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>indah nyaman sayang amen</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2856,19 +2856,19 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>If you're lucky, you can catch a sunset like this from here. Hopefully, in the future, it will be tidier and cleaner. Some spots still need more attention. ð â¦</t>
+          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2878,22 +2878,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>if youre lucky you can catch a sunset like this from here hopefully in the future it will be tidier and cleaner some spots still need more attention ð â</t>
+          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['if', 'youre', 'lucky', 'you', 'can', 'catch', 'a', 'sunset', 'like', 'this', 'from', 'here', 'hopefully', 'in', 'the', 'future', 'it', 'will', 'be', 'tidier', 'and', 'cleaner', 'some', 'spots', 'still', 'need', 'more', 'attention', 'ð', 'â']</t>
+          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['if', 'youre', 'lucky', 'you', 'can', 'catch', 'a', 'sunset', 'like', 'this', 'from', 'here', 'hopefully', 'in', 'the', 'future', 'it', 'will', 'be', 'tidier', 'and', 'cleaner', 'some', 'spots', 'still', 'need', 'more', 'attention', 'ð', 'â']</t>
+          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>if youre lucky you can catch a sunset like this from here hopefully in the future it will be tidier and cleaner some spots still need more attention</t>
+          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2910,42 +2910,42 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
+          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
+          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
+          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
+          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
+          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2962,37 +2962,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3004,42 +3004,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3051,515 +3051,92 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stopped by here because I was attending a friend's wedding, so there was still time so it was quite suitable for walking around. It's just that the timing wasn't right. I came around sunset when the sun was at its hottest. So there weren't â¦</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>stopped by here because i was attending a friends wedding so there was still time so it was quite suitable for walking around its just that the timing wasnt right i came around sunset when the sun was at its hottest so there werent â</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['stopped', 'by', 'here', 'because', 'i', 'was', 'attending', 'a', 'friends', 'wedding', 'so', 'there', 'was', 'still', 'time', 'so', 'it', 'was', 'quite', 'suitable', 'for', 'walking', 'around', 'its', 'just', 'that', 'the', 'timing', 'wasnt', 'right', 'i', 'came', 'around', 'sunset', 'when', 'the', 'sun', 'was', 'at', 'its', 'hottest', 'so', 'there', 'werent', 'â']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['stopped', 'by', 'here', 'because', 'i', 'was', 'attending', 'a', 'friends', 'wedding', 'so', 'there', 'was', 'still', 'time', 'so', 'it', 'was', 'quite', 'suitable', 'for', 'walking', 'around', 'its', 'just', 'that', 'the', 'timing', 'wasnt', 'right', 'i', 'came', 'around', 'sunset', 'when', 'the', 'sun', 'was', 'at', 'its', 'hottest', 'so', 'there', 'werent', 'â']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stopped by here because i was attending a friends wedding so there was still time so it was quite suitable for walking around its just that the timing wasnt right i came around sunset when the sun was at its hottest so there werent</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The beach is located right behind the coal-fired power plant (PLTU). Entrance is 15,000 rupiah for cars and 5,000 rupiah for motorcycles. Parking is free. Facilities include shower rooms (5,000 rupiah), toilets (2,000 rupiah), and gazebos â¦</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>the beach is located right behind the coalfired power plant pltu entrance is rupiah for cars and rupiah for motorcycles parking is free facilities include shower rooms rupiah toilets rupiah and gazebos â</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'located', 'right', 'behind', 'the', 'coalfired', 'power', 'plant', 'pltu', 'entrance', 'is', 'rupiah', 'for', 'cars', 'and', 'rupiah', 'for', 'motorcycles', 'parking', 'is', 'free', 'facilities', 'include', 'shower', 'rooms', 'rupiah', 'toilets', 'rupiah', 'and', 'gazebos', 'â']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'located', 'right', 'behind', 'the', 'coalfired', 'power', 'plant', 'pltu', 'entrance', 'is', 'rupiah', 'for', 'cars', 'and', 'rupiah', 'for', 'motorcycles', 'parking', 'is', 'free', 'facilities', 'include', 'shower', 'rooms', 'rupiah', 'toilets', 'rupiah', 'and', 'gazebos', 'â']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>the beach is located right behind the coalfired power plant pltu entrance is rupiah for cars and rupiah for motorcycles parking is free facilities include shower rooms rupiah toilets rupiah and gazebos</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Pantai Citepus Sukabumi</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>LAND</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>rapih tata buka pagar seng</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>LAND</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Pantai Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Indah dan nyaman, sayang banyak pengamen</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>indah dan nyaman sayang banyak pengamen</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>indah nyaman sayang amen</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Pantai Citepus</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Jangilus Monument</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Jalanya mantap</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>jalanya mantap</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>['jalanya', 'mantap']</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>['jalanya', 'mantap']</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>jala mantap</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Pantai Citepus</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>The price of the accommodation is just a mattress + toilet inside, the price is 400,000 to 600,000 more than the hotel price. Then there is a stall owner in the corner near the tree, the person is very strict, setting the price as he â¦</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he â</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kerennn</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>PantainyÃ  kaya ga terawat yaa...cm sebentar mampir dsni..trs cari pantai yg rada bagusan walaupun jauhh ð â¦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>pantainyã kaya ga terawat yaacm sebentar mampir dsnitrs cari pantai yg rada bagusan walaupun jauhh ð â</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['pantainyã', 'kaya', 'ga', 'terawat', 'yaacm', 'sebentar', 'mampir', 'dsnitrs', 'cari', 'pantai', 'yg', 'rada', 'bagusan', 'walaupun', 'jauhh', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['pantainyã', 'kaya', 'ga', 'terawat', 'yaacm', 'sebentar', 'mampir', 'dsnitrs', 'cari', 'pantai', 'yg', 'rada', 'bagusan', 'jauhh', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>pantainy kaya ga awat yaacm sebentar mampir dsnitrs cari pantai yg rada bagus jauhh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -706,37 +706,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,59 +748,59 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jalanya mantap</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>jalanya mantap</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jala mantap</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
+          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,22 +810,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -842,47 +842,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -894,37 +894,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
+          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
+          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>rapih tata buka pagar seng</t>
+          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,136 +936,136 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>rapih tata buka pagar seng</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Bunga Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>The place is cool and cool and quite clean, but I'm confused about looking for the toilet.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>the place is cool and cool and quite clean but im confused about looking for the toilet</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['the', 'place', 'is', 'cool', 'and', 'cool', 'and', 'quite', 'clean', 'but', 'im', 'confused', 'about', 'looking', 'for', 'the', 'toilet']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['the', 'place', 'is', 'cool', 'and', 'cool', 'and', 'quite', 'clean', 'but', 'im', 'confused', 'about', 'looking', 'for', 'the', 'toilet']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>the place is cool and cool and quite clean but im confused about looking for the toilet</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,47 +1077,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -1129,131 +1129,131 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
+          <t>It's really fun, not too crowded and still clean, the water is cool, the waves aren't too big, perfect for swimming, then in the afternoon we went to the rocks, wow, the sunset was amazing, the food was delicious and not too expensive.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
+          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
+          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
+          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
+          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,89 +1265,89 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1364,37 +1364,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1406,89 +1406,89 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+          <t>Batu Bintang is indeed beautiful, suitable for people who like to see sunsets/sunrises, and in the evening, sometimes we can also see lots of swiftlets flying around, it is really recommended.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,42 +1500,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Susah wf.sama signal.,..</t>
+          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1594,42 +1594,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>My friend's hometown, which is like my own village, really likes the cool and fresh atmosphere of Pelabuhan Ratu. Whether you want to go to the nearby beach or see the mountains, it's the perfect healing spot in southern West Java, not too far from Jakarta. Going forward, we'll try to keep it clean, especially by not littering.</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>my friends hometown which is like my own village really likes the cool and fresh atmosphere of pelabuhan ratu whether you want to go to the nearby beach or see the mountains its the perfect healing spot in southern west java not too far from jakarta going forward well try to keep it clean especially by not littering</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['my', 'friends', 'hometown', 'which', 'is', 'like', 'my', 'own', 'village', 'really', 'likes', 'the', 'cool', 'and', 'fresh', 'atmosphere', 'of', 'pelabuhan', 'ratu', 'whether', 'you', 'want', 'to', 'go', 'to', 'the', 'nearby', 'beach', 'or', 'see', 'the', 'mountains', 'its', 'the', 'perfect', 'healing', 'spot', 'in', 'southern', 'west', 'java', 'not', 'too', 'far', 'from', 'jakarta', 'going', 'forward', 'well', 'try', 'to', 'keep', 'it', 'clean', 'especially', 'by', 'not', 'littering']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['my', 'friends', 'hometown', 'which', 'is', 'like', 'my', 'own', 'village', 'really', 'likes', 'the', 'cool', 'and', 'fresh', 'atmosphere', 'of', 'pelabuhan', 'ratu', 'whether', 'you', 'want', 'to', 'go', 'to', 'the', 'nearby', 'beach', 'or', 'see', 'the', 'mountains', 'its', 'the', 'perfect', 'healing', 'spot', 'in', 'southern', 'west', 'java', 'not', 'too', 'far', 'from', 'jakarta', 'going', 'forward', 'well', 'try', 'to', 'keep', 'it', 'clean', 'especially', 'by', 'not', 'littering']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>my friends hometown which is like my own village really likes the cool and fresh atmosphere of labuh ratu whether you want to go to the nearby beach or see the mountains its the perfect healing spot in southern west java not too far from jakarta going forward well try to keep it clean especially by not littering</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1646,42 +1646,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
@@ -1693,37 +1693,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
+          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
+          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
+          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
+          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
+          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,42 +1782,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>Susah wf.sama signal.,..</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1834,37 +1834,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,136 +1876,136 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
+          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
+          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
+          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2064,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2111,42 +2111,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Muara Citepus Palabuhanratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pantainya kurang terawat,parkirnya berntakan</t>
+          <t>The beach, which is located in Ratu Harbor, has become a tourist attraction, so it is more tidy and equipped with umbrellas and visitor seats.  Rinses and toilets are available and well managed .  Many sellers of young coconut, food and â¦</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pantainya kurang terawatparkirnya berntakan</t>
+          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and â</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
+          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
+          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>pantai terawatparkirnya berntakan</t>
+          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,89 +2158,89 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,12 +2252,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2299,94 +2299,94 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
+          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+          <t>Enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music. Enjoy a young coconut water while enjoying it.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
+          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>lumayan bagusaman anak main pantai</t>
+          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -2398,37 +2398,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
+          <t>Pantainya kurang terawat,parkirnya berntakan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>pantainya kurang terawatparkirnya berntakan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>pantai terawatparkirnya berntakan</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2440,42 +2440,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palabuhan Ratu Square: A Strategic Location with a Cozy Atmosphere Palabuhan Ratu Square is a must-visit destination in Sukabumi. Its strategic location, right in the city center and directly adjacent to the Palabuhan Ratu â¦</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu â</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2487,42 +2487,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2534,12 +2534,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2549,22 +2549,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2581,42 +2581,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>It's really fun, not too crowded and still clean, the water is cool, the waves aren't too big, perfect for swimming, then in the afternoon we went to the rocks, wow, the sunset was amazing, the food was delicious and not too expensive.</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2628,42 +2628,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2675,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>lumayan bagusaman untuk anak main dipantainya</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
+          <t>lumayan bagusaman anak main pantai</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2722,42 +2722,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Palabuhan Ratu Square: A Strategic Location with a Cozy Atmosphere Palabuhan Ratu Square is a must-visit destination in Sukabumi. Its strategic location, right in the city center and directly adjacent to the Palabuhan Ratu â¦</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu â</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2769,42 +2769,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2816,89 +2816,89 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Indah dan nyaman, sayang banyak pengamen</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>indah dan nyaman sayang banyak pengamen</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>indah nyaman sayang amen</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2910,12 +2910,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2962,37 +2962,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3004,12 +3004,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3019,22 +3019,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3051,92 +3051,374 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Indah dan nyaman, sayang banyak pengamen</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>indah dan nyaman sayang banyak pengamen</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>indah nyaman sayang amen</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Smile hill Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Pantai Citepus Sukabumi</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A beautiful beach with a stunning sunset view. Access to the location is adequate for both two- and four-wheeled vehicles, via the national road from Cigombong or the Bocimi toll road (when it is permanently opened). My trip from Bogor via â¦</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>a beautiful beach with a stunning sunset view access to the location is adequate for both two and fourwheeled vehicles via the national road from cigombong or the bocimi toll road when it is permanently opened my trip from bogor via â</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>['a', 'beautiful', 'beach', 'with', 'a', 'stunning', 'sunset', 'view', 'access', 'to', 'the', 'location', 'is', 'adequate', 'for', 'both', 'two', 'and', 'fourwheeled', 'vehicles', 'via', 'the', 'national', 'road', 'from', 'cigombong', 'or', 'the', 'bocimi', 'toll', 'road', 'when', 'it', 'is', 'permanently', 'opened', 'my', 'trip', 'from', 'bogor', 'via', 'â']</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>['a', 'beautiful', 'beach', 'with', 'a', 'stunning', 'sunset', 'view', 'access', 'to', 'the', 'location', 'is', 'adequate', 'for', 'both', 'two', 'and', 'fourwheeled', 'vehicles', 'via', 'the', 'national', 'road', 'from', 'cigombong', 'or', 'the', 'bocimi', 'toll', 'road', 'when', 'it', 'is', 'permanently', 'opened', 'my', 'trip', 'from', 'bogor', 'via', 'â']</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>a beautiful beach with a stunning sunset view access to the location is adequate for both two and fourwheeled vehicles via the national road from cigombong or the bocimi toll road when it is permanently opened my trip from bogor via</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Wisata Alam Pantai Sukawayana</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Jangilus Monument</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>tugu nyah udah pindahin</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The price of the accommodation is just a mattress + toilet inside, the price is 400,000 to 600,000 more than the hotel price. Then there is a stall owner in the corner near the tree, the person is very strict, setting the price as he â¦</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he â</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>It's hard to wf with no signal.,..</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>its hard to wf with no signal</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>its hard to wf with no signal</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,59 +560,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Indah dan nyaman, sayang banyak pengamen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>indah dan nyaman sayang banyak pengamen</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>indah nyaman sayang amen</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PantainyÃ  kaya ga terawat yaa...cm sebentar mampir dsni..trs cari pantai yg rada bagusan walaupun jauhh ð â¦</t>
+          <t>It's really fun, not too crowded and still clean, the water is cool, the waves aren't too big, perfect for swimming, then in the afternoon we went to the rocks, wow, the sunset was amazing, the food was delicious and not too expensive.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pantainyã kaya ga terawat yaacm sebentar mampir dsnitrs cari pantai yg rada bagusan walaupun jauhh ð â</t>
+          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['pantainyã', 'kaya', 'ga', 'terawat', 'yaacm', 'sebentar', 'mampir', 'dsnitrs', 'cari', 'pantai', 'yg', 'rada', 'bagusan', 'walaupun', 'jauhh', 'ð', 'â']</t>
+          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['pantainyã', 'kaya', 'ga', 'terawat', 'yaacm', 'sebentar', 'mampir', 'dsnitrs', 'cari', 'pantai', 'yg', 'rada', 'bagusan', 'jauhh', 'ð', 'â']</t>
+          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pantainy kaya ga awat yaacm sebentar mampir dsnitrs cari pantai yg rada bagus jauhh</t>
+          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kerennn</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,42 +701,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,12 +842,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jalanya mantap</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jalanya mantap</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jala mantap</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -882,49 +882,49 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,42 +936,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,89 +983,89 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>rapih tata buka pagar seng</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Taman Bunga Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The place is cool and cool and quite clean, but I'm confused about looking for the toilet.</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>the place is cool and cool and quite clean but im confused about looking for the toilet</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'cool', 'and', 'cool', 'and', 'quite', 'clean', 'but', 'im', 'confused', 'about', 'looking', 'for', 'the', 'toilet']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'cool', 'and', 'cool', 'and', 'quite', 'clean', 'but', 'im', 'confused', 'about', 'looking', 'for', 'the', 'toilet']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>the place is cool and cool and quite clean but im confused about looking for the toilet</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,47 +1077,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Love the bamboo chairs lined up along this beach. No rental fees; just buy a drink or a young coconut. The view is breathtaking, overlooking the beach and coral reef. It's especially great if you want to watch the sunset while relaxing. There's also a music festival on Saturday nights, which entertains tourists.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -1129,195 +1129,195 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>It's really fun, not too crowded and still clean, the water is cool, the waves aren't too big, perfect for swimming, then in the afternoon we went to the rocks, wow, the sunset was amazing, the food was delicious and not too expensive.</t>
+          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
+          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
+          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
+          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
+          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Baru bisa berkeliling disekitarnya, ga bisa masuk ke Pesanggrahan nya... Pantainya sendiri lumayan bersih sih, mungkin karena dekat Pesanggrahan. Ada free wifi yang juga cepat saat saya akses pagi2 banget</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>baru bisa berkeliling disekitarnya ga bisa masuk ke pesanggrahan nya pantainya sendiri lumayan bersih sih mungkin karena dekat pesanggrahan ada free wifi yang juga cepat saat saya akses pagi banget</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['baru', 'bisa', 'berkeliling', 'disekitarnya', 'ga', 'bisa', 'masuk', 'ke', 'pesanggrahan', 'nya', 'pantainya', 'sendiri', 'lumayan', 'bersih', 'sih', 'mungkin', 'karena', 'dekat', 'pesanggrahan', 'ada', 'free', 'wifi', 'yang', 'juga', 'cepat', 'saat', 'saya', 'akses', 'pagi', 'banget']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['berkeliling', 'disekitarnya', 'ga', 'masuk', 'pesanggrahan', 'nya', 'pantainya', 'lumayan', 'bersih', 'sih', 'pesanggrahan', 'free', 'wifi', 'cepat', 'akses', 'pagi', 'banget']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>keliling sekitar ga masuk pesanggrahan nya pantai lumayan bersih sih pesanggrahan free wifi cepat akses pagi banget</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1327,22 +1327,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1359,42 +1359,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Batu Bintang is indeed beautiful, suitable for people who like to see sunsets/sunrises, and in the evening, sometimes we can also see lots of swiftlets flying around, it is really recommended.</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1547,42 +1547,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1609,22 +1609,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1641,47 +1641,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -1693,37 +1693,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>Palabuhanratu square is a comfortable place to rest or just hang out, because the place is spacious and can be a children's play area, there are many traders selling various snacks, next to it there is a large and comfortable grand mosque for praying, there are also toilets available.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>palabuhanratu square is a comfortable place to rest or just hang out because the place is spacious and can be a childrens play area there are many traders selling various snacks next to it there is a large and comfortable grand mosque for praying there are also toilets available</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
+          <t>['palabuhanratu', 'square', 'is', 'a', 'comfortable', 'place', 'to', 'rest', 'or', 'just', 'hang', 'out', 'because', 'the', 'place', 'is', 'spacious', 'and', 'can', 'be', 'a', 'childrens', 'play', 'area', 'there', 'are', 'many', 'traders', 'selling', 'various', 'snacks', 'next', 'to', 'it', 'there', 'is', 'a', 'large', 'and', 'comfortable', 'grand', 'mosque', 'for', 'praying', 'there', 'are', 'also', 'toilets', 'available']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
+          <t>['palabuhanratu', 'square', 'is', 'a', 'comfortable', 'place', 'to', 'rest', 'or', 'just', 'hang', 'out', 'because', 'the', 'place', 'is', 'spacious', 'and', 'can', 'be', 'a', 'childrens', 'play', 'area', 'there', 'are', 'many', 'traders', 'selling', 'various', 'snacks', 'next', 'to', 'it', 'there', 'is', 'a', 'large', 'and', 'comfortable', 'grand', 'mosque', 'for', 'praying', 'there', 'are', 'also', 'toilets', 'available']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
+          <t>palabuhanratu square is a comfortable place to rest or just hang out because the place is spacious and can be a childrens play area there are many traders selling various snacks next to it there is a large and comfortable grand mosque for praying there are also toilets available</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1787,37 +1787,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Susah wf.sama signal.,..</t>
+          <t>Pantainya kurang terawat,parkirnya berntakan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>pantainya kurang terawatparkirnya berntakan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>pantai terawatparkirnya berntakan</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,12 +1829,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Pantai Twenty Cipatuguran Nuansa nya Kaya Ala-Ala Bali. Tempat nyaman aman &amp; sejuk. Kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benar-benar senggang, â¦</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1844,22 +1844,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>pantai twenty cipatuguran nuansa nya kaya alaala bali tempat nyaman aman sejuk kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benarbenar senggang â</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'tempat', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'ada', 'di', 'pantai', 'seseorang', 'tidak', 'bisa', 'mengumpulkan', 'semua', 'kerang', 'yang', 'indah', 'di', 'pantai', 'aku', 'tampil', 'sebaik', 'mungkin', 'saat', 'aku', 'benarbenar', 'senggang', 'â']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'pantai', 'mengumpulkan', 'kerang', 'indah', 'pantai', 'tampil', 'benarbenar', 'senggang', 'â']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>pantai twenty cipatuguran nuansa nya kaya alaala bal nyaman aman sejuk bebas setia pantai kumpul kerang indah pantai tampil benarbenar senggang</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1876,136 +1876,136 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,106 +2017,106 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Muara Citepus Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The beach, which is located in Ratu Harbor, has become a tourist attraction, so it is more tidy and equipped with umbrellas and visitor seats.  Rinses and toilets are available and well managed .  Many sellers of young coconut, food and â¦</t>
+          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and â</t>
+          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
+          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
+          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and</t>
+          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2158,89 +2158,89 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
+          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
+          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
+          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2299,136 +2299,136 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music. Enjoy a young coconut water while enjoying it.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['enjoy', 'the', 'beach', 'atmosphere', 'in', 'the', 'afternoon', 'while', 'waiting', 'for', 'the', 'sunset', 'accompanied', 'by', 'music', 'enjoy', 'a', 'young', 'coconut', 'water', 'while', 'enjoying', 'it']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>enjoy the beach atmosphere in the afternoon while waiting for the sunset accompanied by music enjoy a young coconut water while enjoying it</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pantainya kurang terawat,parkirnya berntakan</t>
+          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>pantainya kurang terawatparkirnya berntakan</t>
+          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
+          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
+          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>pantai terawatparkirnya berntakan</t>
+          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2487,42 +2487,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
+          <t>First time here ðð I really love watching the waves on the beach, it refreshes my mind. Unfortunately, I left in the afternoon, so it was almost sunset by the time I â¦</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
+          <t>first time here ðð i really love watching the waves on the beach it refreshes my mind unfortunately i left in the afternoon so it was almost sunset by the time i â</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['first', 'time', 'here', 'ðð', 'i', 'really', 'love', 'watching', 'the', 'waves', 'on', 'the', 'beach', 'it', 'refreshes', 'my', 'mind', 'unfortunately', 'i', 'left', 'in', 'the', 'afternoon', 'so', 'it', 'was', 'almost', 'sunset', 'by', 'the', 'time', 'i', 'â']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['first', 'time', 'here', 'ðð', 'i', 'really', 'love', 'watching', 'the', 'waves', 'on', 'the', 'beach', 'it', 'refreshes', 'my', 'mind', 'unfortunately', 'i', 'left', 'in', 'the', 'afternoon', 'so', 'it', 'was', 'almost', 'sunset', 'by', 'the', 'time', 'i', 'â']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
+          <t>first time here i really love watching the waves on the beach it refreshes my mind unfortunately i left in the afternoon so it was almost sunset by the time i</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2534,42 +2534,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,89 +2581,89 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
+          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2722,89 +2722,89 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Palabuhan Ratu Square: A Strategic Location with a Cozy Atmosphere Palabuhan Ratu Square is a must-visit destination in Sukabumi. Its strategic location, right in the city center and directly adjacent to the Palabuhan Ratu â¦</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu â</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2863,42 +2863,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2910,42 +2910,42 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2957,12 +2957,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2972,22 +2972,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3004,12 +3004,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3019,22 +3019,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3051,59 +3051,59 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Indah dan nyaman, sayang banyak pengamen</t>
+          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>indah dan nyaman sayang banyak pengamen</t>
+          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
+          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
+          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>indah nyaman sayang amen</t>
+          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3113,22 +3113,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3137,288 +3137,6 @@
         </is>
       </c>
       <c r="I58" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Pantai Citepus Sukabumi</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>A beautiful beach with a stunning sunset view. Access to the location is adequate for both two- and four-wheeled vehicles, via the national road from Cigombong or the Bocimi toll road (when it is permanently opened). My trip from Bogor via â¦</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>a beautiful beach with a stunning sunset view access to the location is adequate for both two and fourwheeled vehicles via the national road from cigombong or the bocimi toll road when it is permanently opened my trip from bogor via â</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>['a', 'beautiful', 'beach', 'with', 'a', 'stunning', 'sunset', 'view', 'access', 'to', 'the', 'location', 'is', 'adequate', 'for', 'both', 'two', 'and', 'fourwheeled', 'vehicles', 'via', 'the', 'national', 'road', 'from', 'cigombong', 'or', 'the', 'bocimi', 'toll', 'road', 'when', 'it', 'is', 'permanently', 'opened', 'my', 'trip', 'from', 'bogor', 'via', 'â']</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>['a', 'beautiful', 'beach', 'with', 'a', 'stunning', 'sunset', 'view', 'access', 'to', 'the', 'location', 'is', 'adequate', 'for', 'both', 'two', 'and', 'fourwheeled', 'vehicles', 'via', 'the', 'national', 'road', 'from', 'cigombong', 'or', 'the', 'bocimi', 'toll', 'road', 'when', 'it', 'is', 'permanently', 'opened', 'my', 'trip', 'from', 'bogor', 'via', 'â']</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>a beautiful beach with a stunning sunset view access to the location is adequate for both two and fourwheeled vehicles via the national road from cigombong or the bocimi toll road when it is permanently opened my trip from bogor via</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Jangilus Monument</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Tugu nyah udah di pindahin</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>tugu nyah udah di pindahin</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>tugu nyah udah pindahin</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Entrance is free. The view is beautiful, especially at sunset. The food here is standard fare. The mochi is delicious, only around 5,000 rupiah. There's also accommodation nearby, with an Indomaret just a 5-minute walk away. You can also â¦</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,22 +481,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a minute walk away you can also â</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a mute walk away you can also</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>It's hard to wf with no signal.,..</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>its hard to wf with no signal</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>its hard to wf with no signal</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,89 +560,89 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Indah dan nyaman, sayang banyak pengamen</t>
+          <t>PantainyÃ  kaya ga terawat yaa...cm sebentar mampir dsni..trs cari pantai yg rada bagusan walaupun jauhh ð â¦</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>indah dan nyaman sayang banyak pengamen</t>
+          <t>pantainyã kaya ga terawat yaacm sebentar mampir dsnitrs cari pantai yg rada bagusan walaupun jauhh ð â</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
+          <t>['pantainyã', 'kaya', 'ga', 'terawat', 'yaacm', 'sebentar', 'mampir', 'dsnitrs', 'cari', 'pantai', 'yg', 'rada', 'bagusan', 'walaupun', 'jauhh', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
+          <t>['pantainyã', 'kaya', 'ga', 'terawat', 'yaacm', 'sebentar', 'mampir', 'dsnitrs', 'cari', 'pantai', 'yg', 'rada', 'bagusan', 'jauhh', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>indah nyaman sayang amen</t>
+          <t>pantainy kaya ga awat yaacm sebentar mampir dsnitrs cari pantai yg rada bagus jauhh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It's really fun, not too crowded and still clean, the water is cool, the waves aren't too big, perfect for swimming, then in the afternoon we went to the rocks, wow, the sunset was amazing, the food was delicious and not too expensive.</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,89 +654,89 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>Enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya Sawarna yg pasir nya masi putih ðð â¦</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya masi putih ðð â</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'cuma', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>enak sih pantai nya ngga kotor pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya mas putih</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,12 +842,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -882,96 +882,96 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>This the best place to hangout day or night doesn't' matter, there are street performer, food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>this the best place to hangout day or night doesnt matter there are street performer food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+          <t>['this', 'the', 'best', 'place', 'to', 'hangout', 'day', 'or', 'night', 'doesnt', 'matter', 'there', 'are', 'street', 'performer', 'food', 'and', 'drink', 'of', 'course', 'and', 'the', 'best', 'view', 'for', 'sunset', 'too', 'just', 'too', 'bad', 'when', 'night', 'time', 'its', 'too', 'dark', 'for', 'taking', 'selfie', 'or', 'pic', 'here', 'but', 'it', 'never', 'hurt', 'to', 'try', 'visit', 'here']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+          <t>['this', 'the', 'best', 'place', 'to', 'hangout', 'day', 'or', 'night', 'doesnt', 'matter', 'there', 'are', 'street', 'performer', 'food', 'and', 'drink', 'of', 'course', 'and', 'the', 'best', 'view', 'for', 'sunset', 'too', 'just', 'too', 'bad', 'when', 'night', 'time', 'its', 'too', 'dark', 'for', 'taking', 'selfie', 'or', 'pic', 'here', 'but', 'it', 'never', 'hurt', 'to', 'try', 'visit', 'here']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>this the best place to hangout day or night doesnt matter there are street performer food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1023,49 +1023,49 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,12 +1077,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Love the bamboo chairs lined up along this beach. No rental fees; just buy a drink or a young coconut. The view is breathtaking, overlooking the beach and coral reef. It's especially great if you want to watch the sunset while relaxing. There's also a music festival on Saturday nights, which entertains tourists.</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,42 +1124,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
+          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
+          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
+          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baru bisa berkeliling disekitarnya, ga bisa masuk ke Pesanggrahan nya... Pantainya sendiri lumayan bersih sih, mungkin karena dekat Pesanggrahan. Ada free wifi yang juga cepat saat saya akses pagi2 banget</t>
+          <t>The beach's proximity to the main road and easy access make it a prime choice for exploring. However, it lacks public facilities like showers, toilets, and a prayer room, which still appear to be less than clean.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>baru bisa berkeliling disekitarnya ga bisa masuk ke pesanggrahan nya pantainya sendiri lumayan bersih sih mungkin karena dekat pesanggrahan ada free wifi yang juga cepat saat saya akses pagi banget</t>
+          <t>the beachs proximity to the main road and easy access make it a prime choice for exploring however it lacks public facilities like showers toilets and a prayer room which still appear to be less than clean</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['baru', 'bisa', 'berkeliling', 'disekitarnya', 'ga', 'bisa', 'masuk', 'ke', 'pesanggrahan', 'nya', 'pantainya', 'sendiri', 'lumayan', 'bersih', 'sih', 'mungkin', 'karena', 'dekat', 'pesanggrahan', 'ada', 'free', 'wifi', 'yang', 'juga', 'cepat', 'saat', 'saya', 'akses', 'pagi', 'banget']</t>
+          <t>['the', 'beachs', 'proximity', 'to', 'the', 'main', 'road', 'and', 'easy', 'access', 'make', 'it', 'a', 'prime', 'choice', 'for', 'exploring', 'however', 'it', 'lacks', 'public', 'facilities', 'like', 'showers', 'toilets', 'and', 'a', 'prayer', 'room', 'which', 'still', 'appear', 'to', 'be', 'less', 'than', 'clean']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['berkeliling', 'disekitarnya', 'ga', 'masuk', 'pesanggrahan', 'nya', 'pantainya', 'lumayan', 'bersih', 'sih', 'pesanggrahan', 'free', 'wifi', 'cepat', 'akses', 'pagi', 'banget']</t>
+          <t>['the', 'beachs', 'proximity', 'to', 'the', 'main', 'road', 'and', 'easy', 'access', 'make', 'it', 'a', 'prime', 'choice', 'for', 'exploring', 'however', 'it', 'lacks', 'public', 'facilities', 'like', 'showers', 'toilets', 'and', 'a', 'prayer', 'room', 'which', 'still', 'appear', 'to', 'be', 'less', 'than', 'clean']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>keliling sekitar ga masuk pesanggrahan nya pantai lumayan bersih sih pesanggrahan free wifi cepat akses pagi banget</t>
+          <t>the beachs proximity to the main road and easy access make it a prime choice for exploring however it lacks public facilities like showers toilets and a prayer room which still appear to be less than clean</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,136 +1218,136 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,89 +1359,89 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
+          <t>Indah dan nyaman, sayang banyak pengamen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>indah dan nyaman sayang banyak pengamen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>indah nyaman sayang amen</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1458,37 +1458,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,89 +1500,89 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>The beach is comfortable, clean, there are huts to enjoy the beach atmosphere, in short it's really great, there are lots of food menus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>the beach is comfortable clean there are huts to enjoy the beach atmosphere in short its really great there are lots of food menus</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['the', 'beach', 'is', 'comfortable', 'clean', 'there', 'are', 'huts', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'in', 'short', 'its', 'really', 'great', 'there', 'are', 'lots', 'of', 'food', 'menus']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['the', 'beach', 'is', 'comfortable', 'clean', 'there', 'are', 'huts', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'in', 'short', 'its', 'really', 'great', 'there', 'are', 'lots', 'of', 'food', 'menus']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>the beach is comfortable clean there are huts to enjoy the beach atmosphere in short its really great there are lots of food nus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1594,89 +1594,89 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
+          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
+          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
+          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
+          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
+          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
+          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1688,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Palabuhanratu square is a comfortable place to rest or just hang out, because the place is spacious and can be a children's play area, there are many traders selling various snacks, next to it there is a large and comfortable grand mosque for praying, there are also toilets available.</t>
+          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>palabuhanratu square is a comfortable place to rest or just hang out because the place is spacious and can be a childrens play area there are many traders selling various snacks next to it there is a large and comfortable grand mosque for praying there are also toilets available</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'a', 'comfortable', 'place', 'to', 'rest', 'or', 'just', 'hang', 'out', 'because', 'the', 'place', 'is', 'spacious', 'and', 'can', 'be', 'a', 'childrens', 'play', 'area', 'there', 'are', 'many', 'traders', 'selling', 'various', 'snacks', 'next', 'to', 'it', 'there', 'is', 'a', 'large', 'and', 'comfortable', 'grand', 'mosque', 'for', 'praying', 'there', 'are', 'also', 'toilets', 'available']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'a', 'comfortable', 'place', 'to', 'rest', 'or', 'just', 'hang', 'out', 'because', 'the', 'place', 'is', 'spacious', 'and', 'can', 'be', 'a', 'childrens', 'play', 'area', 'there', 'are', 'many', 'traders', 'selling', 'various', 'snacks', 'next', 'to', 'it', 'there', 'is', 'a', 'large', 'and', 'comfortable', 'grand', 'mosque', 'for', 'praying', 'there', 'are', 'also', 'toilets', 'available']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>palabuhanratu square is a comfortable place to rest or just hang out because the place is spacious and can be a childrens play area there are many traders selling various snacks next to it there is a large and comfortable grand mosque for praying there are also toilets available</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,42 +1782,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pantainya kurang terawat,parkirnya berntakan</t>
+          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pantainya kurang terawatparkirnya berntakan</t>
+          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pantainya', 'kurang', 'terawatparkirnya', 'berntakan']</t>
+          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pantainya', 'terawatparkirnya', 'berntakan']</t>
+          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pantai terawatparkirnya berntakan</t>
+          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,12 +1829,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran Nuansa nya Kaya Ala-Ala Bali. Tempat nyaman aman &amp; sejuk. Kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benar-benar senggang, â¦</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1844,22 +1844,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>pantai twenty cipatuguran nuansa nya kaya alaala bali tempat nyaman aman sejuk kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benarbenar senggang â</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'tempat', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'ada', 'di', 'pantai', 'seseorang', 'tidak', 'bisa', 'mengumpulkan', 'semua', 'kerang', 'yang', 'indah', 'di', 'pantai', 'aku', 'tampil', 'sebaik', 'mungkin', 'saat', 'aku', 'benarbenar', 'senggang', 'â']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'pantai', 'mengumpulkan', 'kerang', 'indah', 'pantai', 'tampil', 'benarbenar', 'senggang', 'â']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>pantai twenty cipatuguran nuansa nya kaya alaala bal nyaman aman sejuk bebas setia pantai kumpul kerang indah pantai tampil benarbenar senggang</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1876,59 +1876,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1963,19 +1963,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2017,59 +2017,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>It's really fun, not too crowded and still clean, the water is cool, the waves aren't too big, perfect for swimming, then in the afternoon we went to the rocks, wow, the sunset was amazing, the food was delicious and not too expensive.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2111,42 +2111,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
+          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,89 +2158,89 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>kali lapang cangehgarbagus</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,42 +2252,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Palabuhan Ratu Square: A Strategic Location with a Cozy Atmosphere Palabuhan Ratu Square is a must-visit destination in Sukabumi. Its strategic location, right in the city center and directly adjacent to the Palabuhan Ratu â¦</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu â</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,47 +2299,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
@@ -2351,37 +2351,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,42 +2393,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+          <t>The price of the accommodation is just a mattress + toilet inside, the price is 400,000 to 600,000 more than the hotel price. Then there is a stall owner in the corner near the tree, the person is very strict, setting the price as he â¦</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he â</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2487,42 +2487,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>First time here ðð I really love watching the waves on the beach, it refreshes my mind. Unfortunately, I left in the afternoon, so it was almost sunset by the time I â¦</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>first time here ðð i really love watching the waves on the beach it refreshes my mind unfortunately i left in the afternoon so it was almost sunset by the time i â</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['first', 'time', 'here', 'ðð', 'i', 'really', 'love', 'watching', 'the', 'waves', 'on', 'the', 'beach', 'it', 'refreshes', 'my', 'mind', 'unfortunately', 'i', 'left', 'in', 'the', 'afternoon', 'so', 'it', 'was', 'almost', 'sunset', 'by', 'the', 'time', 'i', 'â']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['first', 'time', 'here', 'ðð', 'i', 'really', 'love', 'watching', 'the', 'waves', 'on', 'the', 'beach', 'it', 'refreshes', 'my', 'mind', 'unfortunately', 'i', 'left', 'in', 'the', 'afternoon', 'so', 'it', 'was', 'almost', 'sunset', 'by', 'the', 'time', 'i', 'â']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>first time here i really love watching the waves on the beach it refreshes my mind unfortunately i left in the afternoon so it was almost sunset by the time i</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2534,42 +2534,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,59 +2581,59 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
+          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2643,22 +2643,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
+          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
+          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2675,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>lumayan bagusaman anak main pantai</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2722,59 +2722,59 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2816,42 +2816,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2863,42 +2863,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2910,12 +2910,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Beautiful beach near the Plabuhan Ratu power plant with waves that are not too big, there are nice and comfortable huts, the price of renting a hut is 150k, there is a prayer room and public toilets, there is something interesting about the â¦</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>beautiful beach near the plabuhan ratu power plant with waves that are not too big there are nice and comfortable huts the price of renting a hut is k there is a prayer room and public toilets there is something interesting about the â</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['beautiful', 'beach', 'near', 'the', 'plabuhan', 'ratu', 'power', 'plant', 'with', 'waves', 'that', 'are', 'not', 'too', 'big', 'there', 'are', 'nice', 'and', 'comfortable', 'huts', 'the', 'price', 'of', 'renting', 'a', 'hut', 'is', 'k', 'there', 'is', 'a', 'prayer', 'room', 'and', 'public', 'toilets', 'there', 'is', 'something', 'interesting', 'about', 'the', 'â']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['beautiful', 'beach', 'near', 'the', 'plabuhan', 'ratu', 'power', 'plant', 'with', 'waves', 'that', 'are', 'not', 'too', 'big', 'there', 'are', 'nice', 'and', 'comfortable', 'huts', 'the', 'price', 'of', 'renting', 'a', 'hut', 'is', 'k', 'there', 'is', 'a', 'prayer', 'room', 'and', 'public', 'toilets', 'there', 'is', 'something', 'interesting', 'about', 'the', 'â']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>beautiful beach near the plabuhan ratu power plant with waves that are not too big there are nice and comfortable huts the price of renting a hut is k there is a prayer room and public toilets there is something interesting about the</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2957,42 +2957,42 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3004,12 +3004,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tugu nyah udah di pindahin</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3019,22 +3019,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tugu nyah udah di pindahin</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>tugu nyah udah pindahin</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3051,59 +3051,59 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Banyak penjual tp harga masih masuk akal,parkiran terbatas,ada mushola,klo mau mandi dipantai harus extra hati" karena bentuk pantai nya tidak landai dam byk karang</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>banyak penjual tp harga masih masuk akalparkiran terbatasada musholaklo mau mandi dipantai harus extra hati karena bentuk pantai nya tidak landai dam byk karang</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['banyak', 'penjual', 'tp', 'harga', 'masih', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mau', 'mandi', 'dipantai', 'harus', 'extra', 'hati', 'karena', 'bentuk', 'pantai', 'nya', 'tidak', 'landai', 'dam', 'byk', 'karang']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['penjual', 'tp', 'harga', 'masuk', 'akalparkiran', 'terbatasada', 'musholaklo', 'mandi', 'dipantai', 'extra', 'hati', 'bentuk', 'pantai', 'nya', 'landai', 'dam', 'byk', 'karang']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>jual tp harga masuk akalparkiran terbatasada musholaklo mandi pantai extra hati bentuk pantai nya landai dam byk karang</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3113,22 +3113,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>lumayan bagusaman untuk anak main dipantainya</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>lumayan bagusaman anak main pantai</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3137,6 +3137,382 @@
         </is>
       </c>
       <c r="I58" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>kali lapang cangehgarbagus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Taman Bunga Gunung Sumping</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>cocok jalanjalan santai ramai sejuk</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Waterpark Citepus Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Taman Bunga Gunung Sumping</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entrance is free. The view is beautiful, especially at sunset. The food here is standard fare. The mochi is delicious, only around 5,000 rupiah. There's also accommodation nearby, with an Indomaret just a 5-minute walk away. You can also â¦</t>
+          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a minute walk away you can also â</t>
+          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a mute walk away you can also</t>
+          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PantainyÃ  kaya ga terawat yaa...cm sebentar mampir dsni..trs cari pantai yg rada bagusan walaupun jauhh ð â¦</t>
+          <t>First time here ðð I really love watching the waves on the beach, it refreshes my mind. Unfortunately, I left in the afternoon, so it was almost sunset by the time I â¦</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,22 +575,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantainyã kaya ga terawat yaacm sebentar mampir dsnitrs cari pantai yg rada bagusan walaupun jauhh ð â</t>
+          <t>first time here ðð i really love watching the waves on the beach it refreshes my mind unfortunately i left in the afternoon so it was almost sunset by the time i â</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantainyã', 'kaya', 'ga', 'terawat', 'yaacm', 'sebentar', 'mampir', 'dsnitrs', 'cari', 'pantai', 'yg', 'rada', 'bagusan', 'walaupun', 'jauhh', 'ð', 'â']</t>
+          <t>['first', 'time', 'here', 'ðð', 'i', 'really', 'love', 'watching', 'the', 'waves', 'on', 'the', 'beach', 'it', 'refreshes', 'my', 'mind', 'unfortunately', 'i', 'left', 'in', 'the', 'afternoon', 'so', 'it', 'was', 'almost', 'sunset', 'by', 'the', 'time', 'i', 'â']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantainyã', 'kaya', 'ga', 'terawat', 'yaacm', 'sebentar', 'mampir', 'dsnitrs', 'cari', 'pantai', 'yg', 'rada', 'bagusan', 'jauhh', 'ð', 'â']</t>
+          <t>['first', 'time', 'here', 'ðð', 'i', 'really', 'love', 'watching', 'the', 'waves', 'on', 'the', 'beach', 'it', 'refreshes', 'my', 'mind', 'unfortunately', 'i', 'left', 'in', 'the', 'afternoon', 'so', 'it', 'was', 'almost', 'sunset', 'by', 'the', 'time', 'i', 'â']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantainy kaya ga awat yaacm sebentar mampir dsnitrs cari pantai yg rada bagus jauhh</t>
+          <t>first time here i really love watching the waves on the beach it refreshes my mind unfortunately i left in the afternoon so it was almost sunset by the time i</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
+          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -647,66 +647,66 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kerennn</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya Sawarna yg pasir nya masi putih ðð â¦</t>
+          <t>Love the bamboo chairs lined up along this beach. No rental fees; just buy a drink or a young coconut. The view is breathtaking, overlooking the beach and coral reef. It's especially great if you want to watch the sunset while relaxing. There's also a music festival on Saturday nights, which entertains tourists.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya masi putih ðð â</t>
+          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'cuma', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
+          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
+          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>enak sih pantai nya ngga kotor pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya mas putih</t>
+          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,94 +842,94 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -941,54 +941,54 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>This the best place to hangout day or night doesn't' matter, there are street performer, food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here.</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>this the best place to hangout day or night doesnt matter there are street performer food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['this', 'the', 'best', 'place', 'to', 'hangout', 'day', 'or', 'night', 'doesnt', 'matter', 'there', 'are', 'street', 'performer', 'food', 'and', 'drink', 'of', 'course', 'and', 'the', 'best', 'view', 'for', 'sunset', 'too', 'just', 'too', 'bad', 'when', 'night', 'time', 'its', 'too', 'dark', 'for', 'taking', 'selfie', 'or', 'pic', 'here', 'but', 'it', 'never', 'hurt', 'to', 'try', 'visit', 'here']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['this', 'the', 'best', 'place', 'to', 'hangout', 'day', 'or', 'night', 'doesnt', 'matter', 'there', 'are', 'street', 'performer', 'food', 'and', 'drink', 'of', 'course', 'and', 'the', 'best', 'view', 'for', 'sunset', 'too', 'just', 'too', 'bad', 'when', 'night', 'time', 'its', 'too', 'dark', 'for', 'taking', 'selfie', 'or', 'pic', 'here', 'but', 'it', 'never', 'hurt', 'to', 'try', 'visit', 'here']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>this the best place to hangout day or night doesnt matter there are street performer food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>The price of the accommodation is just a mattress + toilet inside, the price is 400,000 to 600,000 more than the hotel price. Then there is a stall owner in the corner near the tree, the person is very strict, setting the price as he â¦</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he â</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,12 +1077,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,89 +1124,89 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+          <t>The place is beautiful at sunset..that's the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The beach's proximity to the main road and easy access make it a prime choice for exploring. However, it lacks public facilities like showers, toilets, and a prayer room, which still appear to be less than clean.</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>the beachs proximity to the main road and easy access make it a prime choice for exploring however it lacks public facilities like showers toilets and a prayer room which still appear to be less than clean</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['the', 'beachs', 'proximity', 'to', 'the', 'main', 'road', 'and', 'easy', 'access', 'make', 'it', 'a', 'prime', 'choice', 'for', 'exploring', 'however', 'it', 'lacks', 'public', 'facilities', 'like', 'showers', 'toilets', 'and', 'a', 'prayer', 'room', 'which', 'still', 'appear', 'to', 'be', 'less', 'than', 'clean']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['the', 'beachs', 'proximity', 'to', 'the', 'main', 'road', 'and', 'easy', 'access', 'make', 'it', 'a', 'prime', 'choice', 'for', 'exploring', 'however', 'it', 'lacks', 'public', 'facilities', 'like', 'showers', 'toilets', 'and', 'a', 'prayer', 'room', 'which', 'still', 'appear', 'to', 'be', 'less', 'than', 'clean']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>the beachs proximity to the main road and easy access make it a prime choice for exploring however it lacks public facilities like showers toilets and a prayer room which still appear to be less than clean</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,136 +1218,136 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
+          <t>Indah dan nyaman, sayang banyak pengamen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
+          <t>indah dan nyaman sayang banyak pengamen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
+          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
+          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
+          <t>indah nyaman sayang amen</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>Beautiful beach near the Plabuhan Ratu power plant with waves that are not too big, there are nice and comfortable huts, the price of renting a hut is 150k, there is a prayer room and public toilets, there is something interesting about the â¦</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>beautiful beach near the plabuhan ratu power plant with waves that are not too big there are nice and comfortable huts the price of renting a hut is k there is a prayer room and public toilets there is something interesting about the â</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['beautiful', 'beach', 'near', 'the', 'plabuhan', 'ratu', 'power', 'plant', 'with', 'waves', 'that', 'are', 'not', 'too', 'big', 'there', 'are', 'nice', 'and', 'comfortable', 'huts', 'the', 'price', 'of', 'renting', 'a', 'hut', 'is', 'k', 'there', 'is', 'a', 'prayer', 'room', 'and', 'public', 'toilets', 'there', 'is', 'something', 'interesting', 'about', 'the', 'â']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['beautiful', 'beach', 'near', 'the', 'plabuhan', 'ratu', 'power', 'plant', 'with', 'waves', 'that', 'are', 'not', 'too', 'big', 'there', 'are', 'nice', 'and', 'comfortable', 'huts', 'the', 'price', 'of', 'renting', 'a', 'hut', 'is', 'k', 'there', 'is', 'a', 'prayer', 'room', 'and', 'public', 'toilets', 'there', 'is', 'something', 'interesting', 'about', 'the', 'â']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>beautiful beach near the plabuhan ratu power plant with waves that are not too big there are nice and comfortable huts the price of renting a hut is k there is a prayer room and public toilets there is something interesting about the</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Indah dan nyaman, sayang banyak pengamen</t>
+          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>indah dan nyaman sayang banyak pengamen</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>indah nyaman sayang amen</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1399,49 +1399,49 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1500,89 +1500,89 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The beach is comfortable, clean, there are huts to enjoy the beach atmosphere, in short it's really great, there are lots of food menus</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>the beach is comfortable clean there are huts to enjoy the beach atmosphere in short its really great there are lots of food menus</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'comfortable', 'clean', 'there', 'are', 'huts', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'in', 'short', 'its', 'really', 'great', 'there', 'are', 'lots', 'of', 'food', 'menus']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'comfortable', 'clean', 'there', 'are', 'huts', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'in', 'short', 'its', 'really', 'great', 'there', 'are', 'lots', 'of', 'food', 'menus']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>the beach is comfortable clean there are huts to enjoy the beach atmosphere in short its really great there are lots of food nus</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1594,89 +1594,89 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1688,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>Pantai Twenty Cipatuguran Nuansa nya Kaya Ala-Ala Bali. Tempat nyaman aman &amp; sejuk. Kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benar-benar senggang, â¦</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>pantai twenty cipatuguran nuansa nya kaya alaala bali tempat nyaman aman sejuk kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benarbenar senggang â</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'tempat', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'ada', 'di', 'pantai', 'seseorang', 'tidak', 'bisa', 'mengumpulkan', 'semua', 'kerang', 'yang', 'indah', 'di', 'pantai', 'aku', 'tampil', 'sebaik', 'mungkin', 'saat', 'aku', 'benarbenar', 'senggang', 'â']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'pantai', 'mengumpulkan', 'kerang', 'indah', 'pantai', 'tampil', 'benarbenar', 'senggang', 'â']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>pantai twenty cipatuguran nuansa nya kaya alaala bal nyaman aman sejuk bebas setia pantai kumpul kerang indah pantai tampil benarbenar senggang</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1782,136 +1782,136 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tugu nyah udah di pindahin</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tugu nyah udah di pindahin</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tugu nyah udah pindahin</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,42 +1923,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1970,59 +1970,59 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung 150k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â¦</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>pantai yang indah dekat pltu plabuhan ratu dengan ombak tidak terlalu besar terdapat saung saung bagus dan nyaman harga sewa saung k ada musola dan wc umum terdapat yg menarik dari pantai yaitu batu penghalang pantai yg di buat oleh pltu â</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['pantai', 'yang', 'indah', 'dekat', 'pltu', 'plabuhan', 'ratu', 'dengan', 'ombak', 'tidak', 'terlalu', 'besar', 'terdapat', 'saung', 'saung', 'bagus', 'dan', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'ada', 'musola', 'dan', 'wc', 'umum', 'terdapat', 'yg', 'menarik', 'dari', 'pantai', 'yaitu', 'batu', 'penghalang', 'pantai', 'yg', 'di', 'buat', 'oleh', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pantai', 'indah', 'pltu', 'plabuhan', 'ratu', 'ombak', 'saung', 'saung', 'bagus', 'nyaman', 'harga', 'sewa', 'saung', 'k', 'musola', 'wc', 'yg', 'menarik', 'pantai', 'batu', 'penghalang', 'pantai', 'yg', 'pltu', 'â']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pantai indah pltu plabuhan ratu ombak saung saung bagus nyaman harga sewa saung k musola wc yg tarik pantai batu halang pantai yg pltu</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>It's really fun, not too crowded and still clean, the water is cool, the waves aren't too big, perfect for swimming, then in the afternoon we went to the rocks, wow, the sunset was amazing, the food was delicious and not too expensive.</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['its', 'really', 'fun', 'not', 'too', 'crowded', 'and', 'still', 'clean', 'the', 'water', 'is', 'cool', 'the', 'waves', 'arent', 'too', 'big', 'perfect', 'for', 'swimming', 'then', 'in', 'the', 'afternoon', 'we', 'went', 'to', 'the', 'rocks', 'wow', 'the', 'sunset', 'was', 'amazing', 'the', 'food', 'was', 'delicious', 'and', 'not', 'too', 'expensive']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>its really fun not too crowded and still clean the water is cool the waves arent too big perfect for swimming then in the afternoon we went to the rocks wow the sunset was amazing the food was delicious and not too expensive</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2064,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2116,37 +2116,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A special place to enjoy the beach atmosphere and fresh seafood with your family, featuring authentic South Coast flavors. Ample parking and affordable food.</t>
+          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['a', 'special', 'place', 'to', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'fresh', 'seafood', 'with', 'your', 'family', 'featuring', 'authentic', 'south', 'coast', 'flavors', 'ample', 'parking', 'and', 'affordable', 'food']</t>
+          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>a special place to enjoy the beach atmosphere and fresh seafood with your family featuring authentic south coast flavors ample parking and affordable food</t>
+          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2198,96 +2198,96 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
+          <t>Bagus cm tmpat smpah sedikit.. ama pedagang julid ge bnyk Parkir liar bnyk View lumayan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
+          <t>bagus cm tmpat smpah sedikit ama pedagang julid ge bnyk parkir liar bnyk view lumayan</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
+          <t>['bagus', 'cm', 'tmpat', 'smpah', 'sedikit', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
+          <t>['bagus', 'cm', 'tmpat', 'smpah', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
+          <t>bagus cm tmpat smpah ama dagang julid ge bnyk parkir liar bnyk view lumayan</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palabuhan Ratu Square: A Strategic Location with a Cozy Atmosphere Palabuhan Ratu Square is a must-visit destination in Sukabumi. Its strategic location, right in the city center and directly adjacent to the Palabuhan Ratu â¦</t>
+          <t>Come on Tuesday at 5 o'clock, entry is free, just pay 5 thousand for parking. Watch the fishermen set sail. Enjoy the sunset. I like it, I like it.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu â</t>
+          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
+          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['palabuhan', 'ratu', 'square', 'a', 'strategic', 'location', 'with', 'a', 'cozy', 'atmosphere', 'palabuhan', 'ratu', 'square', 'is', 'a', 'mustvisit', 'destination', 'in', 'sukabumi', 'its', 'strategic', 'location', 'right', 'in', 'the', 'city', 'center', 'and', 'directly', 'adjacent', 'to', 'the', 'palabuhan', 'ratu', 'â']</t>
+          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>palabuhan ratu square a strategic location with a cozy atmosphere palabuhan ratu square is a mustvisit destination in sukabumi its strategic location right in the city center and directly adjacent to the palabuhan ratu</t>
+          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,47 +2299,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+          <t>It's hard to wf with no signal.,..</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+          <t>its hard to wf with no signal</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+          <t>its hard to wf with no signal</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -2351,54 +2351,54 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The price of the accommodation is just a mattress + toilet inside, the price is 400,000 to 600,000 more than the hotel price. Then there is a stall owner in the corner near the tree, the person is very strict, setting the price as he â¦</t>
+          <t>The beach's proximity to the main road and easy access make it a prime choice for exploring. However, it lacks public facilities like showers, toilets, and a prayer room, which still appear to be less than clean.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he â</t>
+          <t>the beachs proximity to the main road and easy access make it a prime choice for exploring however it lacks public facilities like showers toilets and a prayer room which still appear to be less than clean</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
+          <t>['the', 'beachs', 'proximity', 'to', 'the', 'main', 'road', 'and', 'easy', 'access', 'make', 'it', 'a', 'prime', 'choice', 'for', 'exploring', 'however', 'it', 'lacks', 'public', 'facilities', 'like', 'showers', 'toilets', 'and', 'a', 'prayer', 'room', 'which', 'still', 'appear', 'to', 'be', 'less', 'than', 'clean']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
+          <t>['the', 'beachs', 'proximity', 'to', 'the', 'main', 'road', 'and', 'easy', 'access', 'make', 'it', 'a', 'prime', 'choice', 'for', 'exploring', 'however', 'it', 'lacks', 'public', 'facilities', 'like', 'showers', 'toilets', 'and', 'a', 'prayer', 'room', 'which', 'still', 'appear', 'to', 'be', 'less', 'than', 'clean']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he</t>
+          <t>the beachs proximity to the main road and easy access make it a prime choice for exploring however it lacks public facilities like showers toilets and a prayer room which still appear to be less than clean</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2440,42 +2440,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2487,42 +2487,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Susah wf.sama signal.,..</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2534,42 +2534,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,42 +2581,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2633,37 +2633,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
+          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
+          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
+          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2675,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2722,89 +2722,89 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2816,42 +2816,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2863,42 +2863,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2910,12 +2910,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Beautiful beach near the Plabuhan Ratu power plant with waves that are not too big, there are nice and comfortable huts, the price of renting a hut is 150k, there is a prayer room and public toilets, there is something interesting about the â¦</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>beautiful beach near the plabuhan ratu power plant with waves that are not too big there are nice and comfortable huts the price of renting a hut is k there is a prayer room and public toilets there is something interesting about the â</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['beautiful', 'beach', 'near', 'the', 'plabuhan', 'ratu', 'power', 'plant', 'with', 'waves', 'that', 'are', 'not', 'too', 'big', 'there', 'are', 'nice', 'and', 'comfortable', 'huts', 'the', 'price', 'of', 'renting', 'a', 'hut', 'is', 'k', 'there', 'is', 'a', 'prayer', 'room', 'and', 'public', 'toilets', 'there', 'is', 'something', 'interesting', 'about', 'the', 'â']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['beautiful', 'beach', 'near', 'the', 'plabuhan', 'ratu', 'power', 'plant', 'with', 'waves', 'that', 'are', 'not', 'too', 'big', 'there', 'are', 'nice', 'and', 'comfortable', 'huts', 'the', 'price', 'of', 'renting', 'a', 'hut', 'is', 'k', 'there', 'is', 'a', 'prayer', 'room', 'and', 'public', 'toilets', 'there', 'is', 'something', 'interesting', 'about', 'the', 'â']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>beautiful beach near the plabuhan ratu power plant with waves that are not too big there are nice and comfortable huts the price of renting a hut is k there is a prayer room and public toilets there is something interesting about the</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2950,96 +2950,96 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
+          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
+          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
+          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3051,89 +3051,89 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>lumayan bagusaman anak main pantai</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3145,89 +3145,89 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Buka setiap hari, tiket masuk kisaran 20 ribu. Tempat nyaman,luas ,kolam cukup banyak ,  kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia. â¦</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>buka setiap hari tiket masuk kisaran ribu tempat nyamanluas kolam cukup banyak kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia â</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['buka', 'setiap', 'hari', 'tiket', 'masuk', 'kisaran', 'ribu', 'tempat', 'nyamanluas', 'kolam', 'cukup', 'banyak', 'kantin', 'dan', 'tempat', 'sewa', 'ban', 'juga', 'ada', 'tempat', 'berteduh', 'atau', 'bale', 'juga', 'tersedia', 'â']</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['buka', 'tiket', 'masuk', 'kisaran', 'ribu', 'nyamanluas', 'kolam', 'kantin', 'sewa', 'ban', 'berteduh', 'bale', 'tersedia', 'â']</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>buka tiket masuk kisar ribu nyamanluas kolam kantin sewa ban teduh bale sedia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+          <t>The beach is clean, and the photo spots are beautiful, with lots of coral reefs. Swimming is also fun and safe. There are also gazebos along the shore that can be rented for resting. However, the toilets here are not very good.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>kali lapang cangehgarbagus</t>
+          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>Entrance is free. The view is beautiful, especially at sunset. The food here is standard fare. The mochi is delicious, only around 5,000 rupiah. There's also accommodation nearby, with an Indomaret just a 5-minute walk away. You can also â¦</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3254,22 +3254,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a minute walk away you can also â</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a mute walk away you can also</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3286,12 +3286,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>If you're lucky, you can catch a sunset like this from here. Hopefully, in the future, it will be tidier and cleaner. Some spots still need more attention. ð â¦</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3301,22 +3301,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>if youre lucky you can catch a sunset like this from here hopefully in the future it will be tidier and cleaner some spots still need more attention ð â</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['if', 'youre', 'lucky', 'you', 'can', 'catch', 'a', 'sunset', 'like', 'this', 'from', 'here', 'hopefully', 'in', 'the', 'future', 'it', 'will', 'be', 'tidier', 'and', 'cleaner', 'some', 'spots', 'still', 'need', 'more', 'attention', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['if', 'youre', 'lucky', 'you', 'can', 'catch', 'a', 'sunset', 'like', 'this', 'from', 'here', 'hopefully', 'in', 'the', 'future', 'it', 'will', 'be', 'tidier', 'and', 'cleaner', 'some', 'spots', 'still', 'need', 'more', 'attention', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>if youre lucky you can catch a sunset like this from here hopefully in the future it will be tidier and cleaner some spots still need more attention</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3333,42 +3333,42 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>lumayan bagusaman untuk anak main dipantainya</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>lumayan bagusaman anak main pantai</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3380,59 +3380,59 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kolam renang terburuk yg pernah saya datangi,sampah berserakan di mana2,keran di kamar ganti nyembur kemana aja,ada pampers dan softex tergeletak di lantai kmr ganti,darah di usap usap di dinding kmar ganti,tempat sampah sangat minim, mie â¦</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>kolam renang terburuk yg pernah saya datangisampah berserakan di manakeran di kamar ganti nyembur kemana ajaada pampers dan softex tergeletak di lantai kmr gantidarah di usap usap di dinding kmar gantitempat sampah sangat minim mie â</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'pernah', 'saya', 'datangisampah', 'berserakan', 'di', 'manakeran', 'di', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'dan', 'softex', 'tergeletak', 'di', 'lantai', 'kmr', 'gantidarah', 'di', 'usap', 'usap', 'di', 'dinding', 'kmar', 'gantitempat', 'sampah', 'sangat', 'minim', 'mie', 'â']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>['kolam', 'renang', 'terburuk', 'yg', 'datangisampah', 'berserakan', 'manakeran', 'kamar', 'ganti', 'nyembur', 'kemana', 'ajaada', 'pampers', 'softex', 'tergeletak', 'lantai', 'kmr', 'gantidarah', 'usap', 'usap', 'dinding', 'kmar', 'gantitempat', 'sampah', 'minim', 'mie', 'â']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>kolam renang buruk yg datangisampah sera manakeran kamar ganti nyembur mana ajaada pampers softex geletak lantai kmr gantidarah usap usap dinding kmar gantitempat sampah minim mie</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3442,22 +3442,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3474,45 +3474,186 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>i-Pe Beach Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ALUN ALUN GADOBANGKONG</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
+          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,12 +560,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First time here ðð I really love watching the waves on the beach, it refreshes my mind. Unfortunately, I left in the afternoon, so it was almost sunset by the time I â¦</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,22 +575,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>first time here ðð i really love watching the waves on the beach it refreshes my mind unfortunately i left in the afternoon so it was almost sunset by the time i â</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['first', 'time', 'here', 'ðð', 'i', 'really', 'love', 'watching', 'the', 'waves', 'on', 'the', 'beach', 'it', 'refreshes', 'my', 'mind', 'unfortunately', 'i', 'left', 'in', 'the', 'afternoon', 'so', 'it', 'was', 'almost', 'sunset', 'by', 'the', 'time', 'i', 'â']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['first', 'time', 'here', 'ðð', 'i', 'really', 'love', 'watching', 'the', 'waves', 'on', 'the', 'beach', 'it', 'refreshes', 'my', 'mind', 'unfortunately', 'i', 'left', 'in', 'the', 'afternoon', 'so', 'it', 'was', 'almost', 'sunset', 'by', 'the', 'time', 'i', 'â']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>first time here i really love watching the waves on the beach it refreshes my mind unfortunately i left in the afternoon so it was almost sunset by the time i</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,89 +607,89 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,89 +701,89 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Pantainya indah banget sumpah, viewnya bikin mata adem, cuma mungkin ombaknya itu bikin ngeri ngeri sedep, jadi kalo anak berenang harus ekstra di awasi ja sih, selebihnya bagus sih, pedagangnya juga ramah ramah, mungkin masih ada beberapa â¦</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>pantainya indah banget sumpah viewnya bikin mata adem cuma mungkin ombaknya itu bikin ngeri ngeri sedep jadi kalo anak berenang harus ekstra di awasi ja sih selebihnya bagus sih pedagangnya juga ramah ramah mungkin masih ada beberapa â</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'cuma', 'mungkin', 'ombaknya', 'itu', 'bikin', 'ngeri', 'ngeri', 'sedep', 'jadi', 'kalo', 'anak', 'berenang', 'harus', 'ekstra', 'di', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'juga', 'ramah', 'ramah', 'mungkin', 'masih', 'ada', 'beberapa', 'â']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['pantainya', 'indah', 'banget', 'sumpah', 'viewnya', 'bikin', 'mata', 'adem', 'ombaknya', 'bikin', 'ngeri', 'ngeri', 'sedep', 'kalo', 'anak', 'berenang', 'ekstra', 'awasi', 'ja', 'sih', 'selebihnya', 'bagus', 'sih', 'pedagangnya', 'ramah', 'ramah', 'â']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>pantai indah banget sumpah viewnya bikin mata adem ombak bikin ngeri ngeri sedep kalo anak renang ekstra awas ja sih lebih bagus sih dagang ramah ramah</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Love the bamboo chairs lined up along this beach. No rental fees; just buy a drink or a young coconut. The view is breathtaking, overlooking the beach and coral reef. It's especially great if you want to watch the sunset while relaxing. There's also a music festival on Saturday nights, which entertains tourists.</t>
+          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,22 +810,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['love', 'the', 'bamboo', 'chairs', 'lined', 'up', 'along', 'this', 'beach', 'no', 'rental', 'fees', 'just', 'buy', 'a', 'drink', 'or', 'a', 'young', 'coconut', 'the', 'view', 'is', 'breathtaking', 'overlooking', 'the', 'beach', 'and', 'coral', 'reef', 'its', 'especially', 'great', 'if', 'you', 'want', 'to', 'watch', 'the', 'sunset', 'while', 'relaxing', 'theres', 'also', 'a', 'music', 'festival', 'on', 'saturday', 'nights', 'which', 'entertains', 'tourists']</t>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>love the bamboo chairs lined up along this beach no rental fees just buy a drink or a young coconut the view is breathtaking overlooking the beach and coral reef its especially great if you want to watch the sunset while relaxing theres also a music festival on saturday nights which entertains tourists</t>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -842,42 +842,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -894,37 +894,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -983,42 +983,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The price of the accommodation is just a mattress + toilet inside, the price is 400,000 to 600,000 more than the hotel price. Then there is a stall owner in the corner near the tree, the person is very strict, setting the price as he â¦</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he â</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['the', 'price', 'of', 'the', 'accommodation', 'is', 'just', 'a', 'mattress', 'toilet', 'inside', 'the', 'price', 'is', 'to', 'more', 'than', 'the', 'hotel', 'price', 'then', 'there', 'is', 'a', 'stall', 'owner', 'in', 'the', 'corner', 'near', 'the', 'tree', 'the', 'person', 'is', 'very', 'strict', 'setting', 'the', 'price', 'as', 'he', 'â']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>the price of the accommodation is just a mattress toilet inside the price is to more than the hotel price then there is a stall owner in the corner near the tree the person is very strict setting the price as he</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,12 +1030,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1082,37 +1082,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
+          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1124,42 +1124,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The place is beautiful at sunset..that's the best time to take pictures hehe</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tugu nyah udah di pindahin</t>
+          <t>Enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya Sawarna yg pasir nya masi putih ðð â¦</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tugu nyah udah di pindahin</t>
+          <t>enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya masi putih ðð â</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'cuma', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tugu nyah udah pindahin</t>
+          <t>enak sih pantai nya ngga kotor pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya mas putih</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,59 +1218,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Indah dan nyaman, sayang banyak pengamen</t>
+          <t>Baru bisa berkeliling disekitarnya, ga bisa masuk ke Pesanggrahan nya... Pantainya sendiri lumayan bersih sih, mungkin karena dekat Pesanggrahan. Ada free wifi yang juga cepat saat saya akses pagi2 banget</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>indah dan nyaman sayang banyak pengamen</t>
+          <t>baru bisa berkeliling disekitarnya ga bisa masuk ke pesanggrahan nya pantainya sendiri lumayan bersih sih mungkin karena dekat pesanggrahan ada free wifi yang juga cepat saat saya akses pagi banget</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
+          <t>['baru', 'bisa', 'berkeliling', 'disekitarnya', 'ga', 'bisa', 'masuk', 'ke', 'pesanggrahan', 'nya', 'pantainya', 'sendiri', 'lumayan', 'bersih', 'sih', 'mungkin', 'karena', 'dekat', 'pesanggrahan', 'ada', 'free', 'wifi', 'yang', 'juga', 'cepat', 'saat', 'saya', 'akses', 'pagi', 'banget']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
+          <t>['berkeliling', 'disekitarnya', 'ga', 'masuk', 'pesanggrahan', 'nya', 'pantainya', 'lumayan', 'bersih', 'sih', 'pesanggrahan', 'free', 'wifi', 'cepat', 'akses', 'pagi', 'banget']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>indah nyaman sayang amen</t>
+          <t>keliling sekitar ga masuk pesanggrahan nya pantai lumayan bersih sih pesanggrahan free wifi cepat akses pagi banget</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1317,37 +1317,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Beautiful beach near the Plabuhan Ratu power plant with waves that are not too big, there are nice and comfortable huts, the price of renting a hut is 150k, there is a prayer room and public toilets, there is something interesting about the â¦</t>
+          <t>This is my second time here after several years. You can get a unique experience here if you come in the afternoon before sunset. There will be millions of bats coming out of their nests.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>beautiful beach near the plabuhan ratu power plant with waves that are not too big there are nice and comfortable huts the price of renting a hut is k there is a prayer room and public toilets there is something interesting about the â</t>
+          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['beautiful', 'beach', 'near', 'the', 'plabuhan', 'ratu', 'power', 'plant', 'with', 'waves', 'that', 'are', 'not', 'too', 'big', 'there', 'are', 'nice', 'and', 'comfortable', 'huts', 'the', 'price', 'of', 'renting', 'a', 'hut', 'is', 'k', 'there', 'is', 'a', 'prayer', 'room', 'and', 'public', 'toilets', 'there', 'is', 'something', 'interesting', 'about', 'the', 'â']</t>
+          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['beautiful', 'beach', 'near', 'the', 'plabuhan', 'ratu', 'power', 'plant', 'with', 'waves', 'that', 'are', 'not', 'too', 'big', 'there', 'are', 'nice', 'and', 'comfortable', 'huts', 'the', 'price', 'of', 'renting', 'a', 'hut', 'is', 'k', 'there', 'is', 'a', 'prayer', 'room', 'and', 'public', 'toilets', 'there', 'is', 'something', 'interesting', 'about', 'the', 'â']</t>
+          <t>['this', 'is', 'my', 'second', 'time', 'here', 'after', 'several', 'years', 'you', 'can', 'get', 'a', 'unique', 'experience', 'here', 'if', 'you', 'come', 'in', 'the', 'afternoon', 'before', 'sunset', 'there', 'will', 'be', 'millions', 'of', 'bats', 'coming', 'out', 'of', 'their', 'nests']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>beautiful beach near the plabuhan ratu power plant with waves that are not too big there are nice and comfortable huts the price of renting a hut is k there is a prayer room and public toilets there is something interesting about the</t>
+          <t>this is my second time here after several years you can get a unique experience here if you come in the afternoon before sunset there will be millions of bats coming out of their nests</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,42 +1359,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1411,54 +1411,54 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Indah dan nyaman, sayang banyak pengamen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>indah dan nyaman sayang banyak pengamen</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['indah', 'dan', 'nyaman', 'sayang', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['indah', 'nyaman', 'sayang', 'pengamen']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>indah nyaman sayang amen</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1493,49 +1493,49 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
+          <t>The place is comfortable, cool, the toilet is always clean. The prayer clothes in the mosque are fragrant and clean. There are many vendors selling unique and cheap snacks, and the taste is also delicious.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
+          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
+          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1609,22 +1609,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1641,12 +1641,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>kali lapang cangehgarbagus</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1688,12 +1688,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1703,22 +1703,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran Nuansa nya Kaya Ala-Ala Bali. Tempat nyaman aman &amp; sejuk. Kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benar-benar senggang, â¦</t>
+          <t>tempat yg indah,penataan yg bagus,tetap jaga kebersihan....</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>pantai twenty cipatuguran nuansa nya kaya alaala bali tempat nyaman aman sejuk kebebasan setia ada di pantai seseorang tidak bisa mengumpulkan semua kerang yang indah di pantai aku tampil sebaik mungkin saat aku benarbenar senggang â</t>
+          <t>tempat yg indahpenataan yg bagustetap jaga kebersihan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'tempat', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'ada', 'di', 'pantai', 'seseorang', 'tidak', 'bisa', 'mengumpulkan', 'semua', 'kerang', 'yang', 'indah', 'di', 'pantai', 'aku', 'tampil', 'sebaik', 'mungkin', 'saat', 'aku', 'benarbenar', 'senggang', 'â']</t>
+          <t>['tempat', 'yg', 'indahpenataan', 'yg', 'bagustetap', 'jaga', 'kebersihan']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['pantai', 'twenty', 'cipatuguran', 'nuansa', 'nya', 'kaya', 'alaala', 'bali', 'nyaman', 'aman', 'sejuk', 'kebebasan', 'setia', 'pantai', 'mengumpulkan', 'kerang', 'indah', 'pantai', 'tampil', 'benarbenar', 'senggang', 'â']</t>
+          <t>['yg', 'indahpenataan', 'yg', 'bagustetap', 'jaga', 'kebersihan']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>pantai twenty cipatuguran nuansa nya kaya alaala bal nyaman aman sejuk bebas setia pantai kumpul kerang indah pantai tampil benarbenar senggang</t>
+          <t>yg indahpenataan yg bagustetap jaga bersih</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1782,12 +1782,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1797,22 +1797,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1822,19 +1822,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1844,22 +1844,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1869,101 +1869,101 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2017,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kerennn</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2064,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2111,42 +2111,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
+          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,42 +2158,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2205,89 +2205,89 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bagus cm tmpat smpah sedikit.. ama pedagang julid ge bnyk Parkir liar bnyk View lumayan</t>
+          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>bagus cm tmpat smpah sedikit ama pedagang julid ge bnyk parkir liar bnyk view lumayan</t>
+          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['bagus', 'cm', 'tmpat', 'smpah', 'sedikit', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['bagus', 'cm', 'tmpat', 'smpah', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
+          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>bagus cm tmpat smpah ama dagang julid ge bnyk parkir liar bnyk view lumayan</t>
+          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Come on Tuesday at 5 o'clock, entry is free, just pay 5 thousand for parking. Watch the fishermen set sail. Enjoy the sunset. I like it, I like it.</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['come', 'on', 'tuesday', 'at', 'oclock', 'entry', 'is', 'free', 'just', 'pay', 'thousand', 'for', 'parking', 'watch', 'the', 'fishermen', 'set', 'sail', 'enjoy', 'the', 'sunset', 'i', 'like', 'it', 'i', 'like', 'it']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>come on tuesday at oclock entry is free just pay thousand for parking watch the fishermen set sail enjoy the sunset i like it i like it</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,42 +2299,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>It's hard to wf with no signal.,..</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>its hard to wf with no signal</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['its', 'hard', 'to', 'wf', 'with', 'no', 'signal']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>its hard to wf with no signal</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2346,12 +2346,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2361,22 +2361,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Muara Citepus Palabuhanratu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The beach's proximity to the main road and easy access make it a prime choice for exploring. However, it lacks public facilities like showers, toilets, and a prayer room, which still appear to be less than clean.</t>
+          <t>The beach, which is located in Ratu Harbor, has become a tourist attraction, so it is more tidy and equipped with umbrellas and visitor seats.  Rinses and toilets are available and well managed .  Many sellers of young coconut, food and â¦</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>the beachs proximity to the main road and easy access make it a prime choice for exploring however it lacks public facilities like showers toilets and a prayer room which still appear to be less than clean</t>
+          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and â</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['the', 'beachs', 'proximity', 'to', 'the', 'main', 'road', 'and', 'easy', 'access', 'make', 'it', 'a', 'prime', 'choice', 'for', 'exploring', 'however', 'it', 'lacks', 'public', 'facilities', 'like', 'showers', 'toilets', 'and', 'a', 'prayer', 'room', 'which', 'still', 'appear', 'to', 'be', 'less', 'than', 'clean']</t>
+          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['the', 'beachs', 'proximity', 'to', 'the', 'main', 'road', 'and', 'easy', 'access', 'make', 'it', 'a', 'prime', 'choice', 'for', 'exploring', 'however', 'it', 'lacks', 'public', 'facilities', 'like', 'showers', 'toilets', 'and', 'a', 'prayer', 'room', 'which', 'still', 'appear', 'to', 'be', 'less', 'than', 'clean']</t>
+          <t>['the', 'beach', 'which', 'is', 'located', 'in', 'ratu', 'harbor', 'has', 'become', 'a', 'tourist', 'attraction', 'so', 'it', 'is', 'more', 'tidy', 'and', 'equipped', 'with', 'umbrellas', 'and', 'visitor', 'seats', 'rinses', 'and', 'toilets', 'are', 'available', 'and', 'well', 'managed', 'many', 'sellers', 'of', 'young', 'coconut', 'food', 'and', 'â']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>the beachs proximity to the main road and easy access make it a prime choice for exploring however it lacks public facilities like showers toilets and a prayer room which still appear to be less than clean</t>
+          <t>the beach which is located in ratu harbor has become a tourist attraction so it is more tidy and equipped with umbrellas and visitor seats rinses and toilets are available and well managed many sellers of young coconut food and</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2445,37 +2445,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2487,42 +2487,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Susah wf.sama signal.,..</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2534,12 +2534,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2549,22 +2549,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2581,89 +2581,89 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Bagus cm tmpat smpah sedikit.. ama pedagang julid ge bnyk Parkir liar bnyk View lumayan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>bagus cm tmpat smpah sedikit ama pedagang julid ge bnyk parkir liar bnyk view lumayan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['bagus', 'cm', 'tmpat', 'smpah', 'sedikit', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['bagus', 'cm', 'tmpat', 'smpah', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>bagus cm tmpat smpah ama dagang julid ge bnyk parkir liar bnyk view lumayan</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
+          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
+          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
+          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
+          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
+          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2675,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Batu Bintang is indeed beautiful, suitable for people who like to see sunsets/sunrises, and in the evening, sometimes we can also see lots of swiftlets flying around, it is really recommended.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2722,12 +2722,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jalanya mantap</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2737,22 +2737,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jalanya mantap</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>jala mantap</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2769,42 +2769,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2816,89 +2816,89 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>The beach atmosphere is extraordinary, although there are still some visitors who are not very good at maintaining cleanliness, but for the rest it is very nice and comfortable here.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>the beach atmosphere is extraordinary although there are still some visitors who are not very good at maintaining cleanliness but for the rest it is very nice and comfortable here</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['the', 'beach', 'atmosphere', 'is', 'extraordinary', 'although', 'there', 'are', 'still', 'some', 'visitors', 'who', 'are', 'not', 'very', 'good', 'at', 'maintaining', 'cleanliness', 'but', 'for', 'the', 'rest', 'it', 'is', 'very', 'nice', 'and', 'comfortable', 'here']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['the', 'beach', 'atmosphere', 'is', 'extraordinary', 'although', 'there', 'are', 'still', 'some', 'visitors', 'who', 'are', 'not', 'very', 'good', 'at', 'maintaining', 'cleanliness', 'but', 'for', 'the', 'rest', 'it', 'is', 'very', 'nice', 'and', 'comfortable', 'here']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>the beach atmosphere is extraordinary although there are still some visitors who are not very good at maintaining cleanliness but for the rest it is very nice and comfortable here</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2910,12 +2910,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2950,96 +2950,96 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>Good. Parking is free. Toilets are 2,000 yen. Degan is 15,000 yen. No entrance fee. The waves are quite big. There are horses and ATVs.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
+          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
+          <t>lumayan bagusaman untuk anak main dipantainya</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
+          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
+          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
+          <t>lumayan bagusaman anak main pantai</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3098,42 +3098,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3145,89 +3145,89 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Buka setiap hari, tiket masuk kisaran 20 ribu. Tempat nyaman,luas ,kolam cukup banyak ,  kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia. â¦</t>
+          <t>This the best place to hangout day or night doesn't' matter, there are street performer, food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>buka setiap hari tiket masuk kisaran ribu tempat nyamanluas kolam cukup banyak kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia â</t>
+          <t>this the best place to hangout day or night doesnt matter there are street performer food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>['buka', 'setiap', 'hari', 'tiket', 'masuk', 'kisaran', 'ribu', 'tempat', 'nyamanluas', 'kolam', 'cukup', 'banyak', 'kantin', 'dan', 'tempat', 'sewa', 'ban', 'juga', 'ada', 'tempat', 'berteduh', 'atau', 'bale', 'juga', 'tersedia', 'â']</t>
+          <t>['this', 'the', 'best', 'place', 'to', 'hangout', 'day', 'or', 'night', 'doesnt', 'matter', 'there', 'are', 'street', 'performer', 'food', 'and', 'drink', 'of', 'course', 'and', 'the', 'best', 'view', 'for', 'sunset', 'too', 'just', 'too', 'bad', 'when', 'night', 'time', 'its', 'too', 'dark', 'for', 'taking', 'selfie', 'or', 'pic', 'here', 'but', 'it', 'never', 'hurt', 'to', 'try', 'visit', 'here']</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>['buka', 'tiket', 'masuk', 'kisaran', 'ribu', 'nyamanluas', 'kolam', 'kantin', 'sewa', 'ban', 'berteduh', 'bale', 'tersedia', 'â']</t>
+          <t>['this', 'the', 'best', 'place', 'to', 'hangout', 'day', 'or', 'night', 'doesnt', 'matter', 'there', 'are', 'street', 'performer', 'food', 'and', 'drink', 'of', 'course', 'and', 'the', 'best', 'view', 'for', 'sunset', 'too', 'just', 'too', 'bad', 'when', 'night', 'time', 'its', 'too', 'dark', 'for', 'taking', 'selfie', 'or', 'pic', 'here', 'but', 'it', 'never', 'hurt', 'to', 'try', 'visit', 'here']</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>buka tiket masuk kisar ribu nyamanluas kolam kantin sewa ban teduh bale sedia</t>
+          <t>this the best place to hangout day or night doesnt matter there are street performer food and drink of course and the best view for sunset too just too bad when night time its too dark for taking selfie or pic here but it never hurt to try visit here</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The beach is clean, and the photo spots are beautiful, with lots of coral reefs. Swimming is also fun and safe. There are also gazebos along the shore that can be rented for resting. However, the toilets here are not very good.</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Entrance is free. The view is beautiful, especially at sunset. The food here is standard fare. The mochi is delicious, only around 5,000 rupiah. There's also accommodation nearby, with an Indomaret just a 5-minute walk away. You can also â¦</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3254,22 +3254,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a minute walk away you can also â</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>['entrance', 'is', 'free', 'the', 'view', 'is', 'beautiful', 'especially', 'at', 'sunset', 'the', 'food', 'here', 'is', 'standard', 'fare', 'the', 'mochi', 'is', 'delicious', 'only', 'around', 'rupiah', 'theres', 'also', 'accommodation', 'nearby', 'with', 'an', 'indomaret', 'just', 'a', 'minute', 'walk', 'away', 'you', 'can', 'also', 'â']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>entrance is free the view is beautiful especially at sunset the food here is standard fare the mochi is delicious only around rupiah theres also accommodation nearby with an indomaret just a mute walk away you can also</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3286,12 +3286,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>If you're lucky, you can catch a sunset like this from here. Hopefully, in the future, it will be tidier and cleaner. Some spots still need more attention. ð â¦</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3301,22 +3301,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>if youre lucky you can catch a sunset like this from here hopefully in the future it will be tidier and cleaner some spots still need more attention ð â</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>['if', 'youre', 'lucky', 'you', 'can', 'catch', 'a', 'sunset', 'like', 'this', 'from', 'here', 'hopefully', 'in', 'the', 'future', 'it', 'will', 'be', 'tidier', 'and', 'cleaner', 'some', 'spots', 'still', 'need', 'more', 'attention', 'ð', 'â']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>['if', 'youre', 'lucky', 'you', 'can', 'catch', 'a', 'sunset', 'like', 'this', 'from', 'here', 'hopefully', 'in', 'the', 'future', 'it', 'will', 'be', 'tidier', 'and', 'cleaner', 'some', 'spots', 'still', 'need', 'more', 'attention', 'ð', 'â']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>if youre lucky you can catch a sunset like this from here hopefully in the future it will be tidier and cleaner some spots still need more attention</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3333,183 +3333,183 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>lumayan bagusaman anak main pantai</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>CANTIKK BGTTT GAA SIIII? ð­ð­ð­ sumpah. ini lok foto nya di dkt penginapan bunda. dri tmpt staycation bisa jalan kaki ksniii. aaaa luvv bgttttt. gratis lg masuk nyað» next time bakal ksni lgð» â¦</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>cantikk bgttt gaa siiii ððð sumpah ini lok foto nya di dkt penginapan bunda dri tmpt staycation bisa jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nyað next time bakal ksni lgð â</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'ini', 'lok', 'foto', 'nya', 'di', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'bisa', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'bakal', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['cantikk', 'bgttt', 'gaa', 'siiii', 'ððð', 'sumpah', 'lok', 'foto', 'nya', 'dkt', 'penginapan', 'bunda', 'dri', 'tmpt', 'staycation', 'jalan', 'kaki', 'ksniii', 'aaaa', 'luvv', 'bgttttt', 'gratis', 'lg', 'masuk', 'nyað', 'next', 'time', 'ksni', 'lgð', 'â']</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
+          <t>cantikk bgttt gaa siiii sumpah lok foto nya dkt inap bunda dri tmpt staycation jalan kaki ksniii aaaa luvv bgttttt gratis lg masuk nya next time ksni lg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3568,12 +3568,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pengamen dan pengemisnya banyak. Untuk pengelola tolong tertibkan pengemisnya. Pengamrnya bikinkan panggung saja untuk mereka.</t>
+          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>pengamen dan pengemisnya banyak untuk pengelola tolong tertibkan pengemisnya pengamrnya bikinkan panggung saja untuk mereka</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>['pengamen', 'dan', 'pengemisnya', 'banyak', 'untuk', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung', 'saja', 'untuk', 'mereka']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>['pengamen', 'pengemisnya', 'pengelola', 'tolong', 'tertibkan', 'pengemisnya', 'pengamrnya', 'bikinkan', 'panggung']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>amen emis kelola tolong tertib emis pengamrnya bikin panggung</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3615,42 +3615,42 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
+          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
+          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
+          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
